--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>46091</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>44582</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>46198</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44909</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>45764</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>46066</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46036</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>46052</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44911</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45973</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45986</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>46007</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45222</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45377</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45406</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46283</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45825</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45845</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44470</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44620</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44627</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44529</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>44845</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45321</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45525</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45279</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45194</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45359</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45694</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>46027</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45894</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45911</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>46036</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45926</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>46127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44529</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45243</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>46085</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>46105</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>45426</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>46112</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45985</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>46135</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46205</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>46211</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45411</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45365</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>46265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>46231</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45784</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46276</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46276</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45490</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45524</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45841</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44459</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44497</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44460</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44488</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44763</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44749</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44470</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>44470</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44638</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44795</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44795</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44791</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44824</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44459</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44459</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44833</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44565</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44874</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44459</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44484</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44469</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44477</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44692</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44774</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44838</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44799</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44862</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44638</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44762</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44551</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44845</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44533</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44484</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>44839</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44839</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44544</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44559</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44489</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44841</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44679</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44679</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>44579</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44732</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>44795</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44578</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44789</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>44748</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44573</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45432</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45258</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44651</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>44826</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45555</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45267</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45672</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45321</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>44893</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45596</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45215</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45148</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45523</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45517</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45351</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44977</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45093</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45671</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45588</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45299</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45021</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45344</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45201</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45478</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45558</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45321</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45344</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45518</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45539</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45736</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45539</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>44747</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45677</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45225</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45231</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45363</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45243</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45321</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45253</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>44889</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44991</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44872</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45173</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45693</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44922</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45398</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45161</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45194</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45513</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>45352</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45664</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45453</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45243</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45362</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45201</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44882</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45623</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45653</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45562</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45547</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44736</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45033</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45229</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45002</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45337</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45223</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45275</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45757</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45085</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45412</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45168</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44742</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45205</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45251</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45019</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45019</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>45310</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44944</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>44834</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45666</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45679</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45513</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45686</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45671</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>44621</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45615</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45155</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45645</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45253</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46029</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45737</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46033</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45618</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>46098</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>44798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45840</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45884</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45481</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45659</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45961</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45621</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44529</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45679</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45264</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45586</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46050</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45884</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45726</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45560</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45181</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45776</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45797</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45259</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>46050</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45637</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45888</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45124</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45314</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46049</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45077</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45588</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45916</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45569</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45297</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45895</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45539</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45894</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45321</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45590</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45245</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45209</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45534</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45896</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>46048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45825</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45898</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45989</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45884</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>46139</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45903</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44796</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45902</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45784</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45379</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>46104</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>46035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>46083</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45905</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>45905</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45611</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>45358</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45908</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>46070</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45440</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>46085</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44928</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46062</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46025</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45799</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46050</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46042</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45910</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45910</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>46057</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45567</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46084</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46083</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46132</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46141</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46141</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45915</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45915</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>46141</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46019</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44515</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45915</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>46037</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45915</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>46105</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>46063</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>46044</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45916</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44641</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>46106</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45266</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45919</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45920</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44684</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45107</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45539</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45923</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45923</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45259</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45923</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44644</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45923</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45939</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>44977</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45569</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45925</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46141</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45537</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45686</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>46062</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>44897</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45925</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45925</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>44762</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>45930</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>46141</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45686</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45334</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>45623</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>46027</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>45539</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>46142</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45972</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45930</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45930</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45930</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45968</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46052</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45933</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45603</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45646</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46146</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44529</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45330</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45937</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45937</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>46146</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>45174</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>45937</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45939</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45251</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45672</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45939</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45245</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>46079</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45939</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45943</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45943</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46148</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45940</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45940</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45943</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45541</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45721</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45167</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>46149</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>46148</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>45520</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>44840</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45930</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46148</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46148</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44964</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45537</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45628</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>45946</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45952</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>46085</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>45537</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45616</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45950</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45953</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45953</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45954</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45742</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45957</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45957</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45575</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45958</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>45958</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>46064</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>46106</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>45960</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45960</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45960</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>45961</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>44746</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>44914</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>44960</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45961</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45960</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45960</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45965</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45737</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46113</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46105</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45397</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45965</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45264</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45618</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45967</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45967</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45967</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45966</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46104</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46155</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45321</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45971</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45971</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44562</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45971</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45971</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45971</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45968</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45973</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45176</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45972</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45973</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45267</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45695</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45974</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45161</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>44461</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45974</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45974</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44807</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45975</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46048</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45264</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46055</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45981</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45603</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45985</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45324</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>44911</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45985</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45985</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45985</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45986</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45986</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>46157</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45588</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45987</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45986</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45988</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45989</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45989</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45992</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45632</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>46159</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45071</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44939</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46162</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45622</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45617</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45639</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45994</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45994</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44519</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>45536</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45999</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45999</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46000</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46167</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46000</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45159</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46000</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>46003</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45737</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>45925</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45646</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45546</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>46009</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45615</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45107</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45107</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45090</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>46010</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>46010</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>44823</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>46010</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>44813</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>46010</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46010</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45310</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>44775</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45551</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45443</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45307</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>46105</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>46052</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>46056</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>46139</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>46105</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45958</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>46027</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>46027</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>46027</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>46027</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45282</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>46031</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46030</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46033</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45665</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>46034</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44638</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46033</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46027</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>46033</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>46036</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>46036</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>46036</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>46036</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>44775</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>44798</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>46042</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>46038</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>46042</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>46042</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>46042</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>46044</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>44544</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>46044</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45625</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45436</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>46175</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>46175</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>46048</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45587</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>46049</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>46048</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51144,7 +51144,7 @@
         <v>45618</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51217,7 +51217,7 @@
         <v>46050</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>45198</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>44790</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>46141</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45302</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>44818</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45097</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>46056</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45399</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>46057</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45618</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>46078</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46128</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52249,7 +52249,7 @@
         <v>45558</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>46027</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>46063</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45772</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>46178</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>46062</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>46062</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>46062</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>46062</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>46064</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>46064</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>46065</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>46178</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>44953</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>46066</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>46066</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46066</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>45217</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>46069</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46070</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46140</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45321</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>45518</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>45518</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>46072</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>46072</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45072</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>46073</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>44700</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>46121</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46073</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>45593</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>46078</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>44818</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>46079</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>46184</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>46184</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45105</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46085</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45968</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>46085</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>46068</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45168</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>46086</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45671</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45672</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>46090</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>46090</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>45176</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45420</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45555</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>44910</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>45236</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45722</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>46070</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45590</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46190</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56465,7 +56465,7 @@
         <v>46190</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45483</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>46189</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>46098</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46191</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>46094</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45672</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45210</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46043</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46191</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>46191</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46191</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>46100</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>46196</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>46195</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>46099</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>44571</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>46098</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>46099</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46195</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>46196</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46195</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>46195</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>46104</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>46198</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45230</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45243</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>46105</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58559,7 +58559,7 @@
         <v>46105</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>46106</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58715,7 +58715,7 @@
         <v>46106</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58793,7 +58793,7 @@
         <v>46198</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>46106</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>45537</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>46105</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>46197</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>46107</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59246,7 +59246,7 @@
         <v>46197</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>46197</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>46140</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>44939</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>44728</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>45575</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>44818</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>46198</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>46050</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>46197</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45317</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60069,7 +60069,7 @@
         <v>44929</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45644</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60215,7 +60215,7 @@
         <v>46112</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60288,7 +60288,7 @@
         <v>46122</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         <v>46122</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>45476</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>46126</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60585,7 +60585,7 @@
         <v>46126</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60663,7 +60663,7 @@
         <v>46244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60741,7 +60741,7 @@
         <v>46125</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45642</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60887,7 +60887,7 @@
         <v>46244</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>44637</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>45119</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>45223</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>46127</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>46129</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>44806</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61413,7 +61413,7 @@
         <v>46199</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61491,7 +61491,7 @@
         <v>46127</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44519</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>44875</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61715,7 +61715,7 @@
         <v>45646</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>46203</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>46133</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45582</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>44841</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45775</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45098</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>46134</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         <v>44459</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>46203</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45567</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45182</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>45194</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62689,7 +62689,7 @@
         <v>46136</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>45595</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45187</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>46029</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>45072</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63064,7 +63064,7 @@
         <v>45329</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>46136</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45257</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45204</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>45888</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>46025</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>45516</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>46139</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>45810</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>46203</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63814,7 +63814,7 @@
         <v>46203</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>46246</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45194</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
         <v>46248</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45349</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>45245</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>44847</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64330,7 +64330,7 @@
         <v>45071</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64403,7 +64403,7 @@
         <v>46248</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64481,7 +64481,7 @@
         <v>46206</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64554,7 +64554,7 @@
         <v>45736</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64627,7 +64627,7 @@
         <v>46208</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>45455</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64778,7 +64778,7 @@
         <v>44930</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64851,7 +64851,7 @@
         <v>46205</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64924,7 +64924,7 @@
         <v>46206</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64997,7 +64997,7 @@
         <v>44517</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65070,7 +65070,7 @@
         <v>45139</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>46206</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45231</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45231</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>45534</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>45392</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65513,7 +65513,7 @@
         <v>44997</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>45002</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>45259</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>45625</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>46209</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>46205</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>44746</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>46212</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
         <v>46211</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66175,7 +66175,7 @@
         <v>45600</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66248,7 +66248,7 @@
         <v>46212</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66326,7 +66326,7 @@
         <v>45232</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66399,7 +66399,7 @@
         <v>45756</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66472,7 +66472,7 @@
         <v>44907</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66550,7 +66550,7 @@
         <v>46212</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>45582</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66701,7 +66701,7 @@
         <v>45744</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66774,7 +66774,7 @@
         <v>45190</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66847,7 +66847,7 @@
         <v>45176</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66925,7 +66925,7 @@
         <v>44866</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66998,7 +66998,7 @@
         <v>45422</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67076,7 +67076,7 @@
         <v>46216</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>46259</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>45516</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67295,7 +67295,7 @@
         <v>45112</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>45334</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         <v>45173</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46258</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67592,7 +67592,7 @@
         <v>45586</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67670,7 +67670,7 @@
         <v>46261</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67748,7 +67748,7 @@
         <v>46261</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67826,7 +67826,7 @@
         <v>45733</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67899,7 +67899,7 @@
         <v>46261</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67972,7 +67972,7 @@
         <v>45525</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68045,7 +68045,7 @@
         <v>45525</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68118,7 +68118,7 @@
         <v>44551</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68191,7 +68191,7 @@
         <v>46265</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45321</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68337,7 +68337,7 @@
         <v>44804</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68410,7 +68410,7 @@
         <v>46265</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68483,7 +68483,7 @@
         <v>46153</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68561,7 +68561,7 @@
         <v>45686</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68634,7 +68634,7 @@
         <v>46164</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68712,7 +68712,7 @@
         <v>46220</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68785,7 +68785,7 @@
         <v>45693</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68863,7 +68863,7 @@
         <v>45666</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68936,7 +68936,7 @@
         <v>46265</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69014,7 +69014,7 @@
         <v>46108</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>44475</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69165,7 +69165,7 @@
         <v>46223</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69238,7 +69238,7 @@
         <v>46223</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69311,7 +69311,7 @@
         <v>46224</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69384,7 +69384,7 @@
         <v>45771</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69457,7 +69457,7 @@
         <v>45112</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69530,7 +69530,7 @@
         <v>45188</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69603,7 +69603,7 @@
         <v>45560</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>45666</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69749,7 +69749,7 @@
         <v>45776</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69822,7 +69822,7 @@
         <v>45776</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69895,7 +69895,7 @@
         <v>45779</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45616</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70046,7 +70046,7 @@
         <v>45782</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70119,7 +70119,7 @@
         <v>45279</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70192,7 +70192,7 @@
         <v>45505</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70265,7 +70265,7 @@
         <v>45782</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70338,7 +70338,7 @@
         <v>46273</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70416,7 +70416,7 @@
         <v>46230</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70489,7 +70489,7 @@
         <v>44799</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70567,7 +70567,7 @@
         <v>46274</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70645,7 +70645,7 @@
         <v>46275</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70723,7 +70723,7 @@
         <v>46274</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70801,7 +70801,7 @@
         <v>46275</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>46274</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>45602</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71030,7 +71030,7 @@
         <v>46233</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71108,7 +71108,7 @@
         <v>45784</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71181,7 +71181,7 @@
         <v>45351</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71254,7 +71254,7 @@
         <v>46276</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71332,7 +71332,7 @@
         <v>45545</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71405,7 +71405,7 @@
         <v>46279</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
         <v>46279</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71556,7 +71556,7 @@
         <v>46276</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71634,7 +71634,7 @@
         <v>45273</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71707,7 +71707,7 @@
         <v>46279</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71785,7 +71785,7 @@
         <v>45505</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71858,7 +71858,7 @@
         <v>45582</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71931,7 +71931,7 @@
         <v>46276</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72009,7 +72009,7 @@
         <v>45702</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72082,7 +72082,7 @@
         <v>46237</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72160,7 +72160,7 @@
         <v>45505</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72233,7 +72233,7 @@
         <v>45428</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72306,7 +72306,7 @@
         <v>46276</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72379,7 +72379,7 @@
         <v>45516</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72452,7 +72452,7 @@
         <v>45789</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72525,7 +72525,7 @@
         <v>46280</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72598,7 +72598,7 @@
         <v>46237</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72676,7 +72676,7 @@
         <v>45789</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72749,7 +72749,7 @@
         <v>45552</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72822,7 +72822,7 @@
         <v>45791</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72895,7 +72895,7 @@
         <v>46237</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>45790</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73041,7 +73041,7 @@
         <v>46280</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73119,7 +73119,7 @@
         <v>45188</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73192,7 +73192,7 @@
         <v>46198</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73270,7 +73270,7 @@
         <v>45518</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73343,7 +73343,7 @@
         <v>46237</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73421,7 +73421,7 @@
         <v>45740</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73499,7 +73499,7 @@
         <v>45793</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>46171</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73655,7 +73655,7 @@
         <v>45793</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73728,7 +73728,7 @@
         <v>45097</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73806,7 +73806,7 @@
         <v>45097</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73884,7 +73884,7 @@
         <v>45518</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73957,7 +73957,7 @@
         <v>45594</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74030,7 +74030,7 @@
         <v>46239</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74103,7 +74103,7 @@
         <v>46239</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74176,7 +74176,7 @@
         <v>46283</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74249,7 +74249,7 @@
         <v>46241</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74327,7 +74327,7 @@
         <v>46241</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74405,7 +74405,7 @@
         <v>45796</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74478,7 +74478,7 @@
         <v>45533</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74551,7 +74551,7 @@
         <v>45796</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74624,7 +74624,7 @@
         <v>45796</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74697,7 +74697,7 @@
         <v>46241</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74775,7 +74775,7 @@
         <v>46162</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74848,7 +74848,7 @@
         <v>46241</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74926,7 +74926,7 @@
         <v>45798</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74999,7 +74999,7 @@
         <v>45799</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75072,7 +75072,7 @@
         <v>46057</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75145,7 +75145,7 @@
         <v>46098</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75218,7 +75218,7 @@
         <v>45555</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75291,7 +75291,7 @@
         <v>45373</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>45803</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75442,7 +75442,7 @@
         <v>45803</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75520,7 +75520,7 @@
         <v>45755</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75593,7 +75593,7 @@
         <v>45623</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75666,7 +75666,7 @@
         <v>45377</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>45813</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45813</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75900,7 +75900,7 @@
         <v>45813</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>45817</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76046,7 +76046,7 @@
         <v>45819</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76119,7 +76119,7 @@
         <v>45821</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76192,7 +76192,7 @@
         <v>45820</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76265,7 +76265,7 @@
         <v>45825</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76338,7 +76338,7 @@
         <v>45825</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76411,7 +76411,7 @@
         <v>45825</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76484,7 +76484,7 @@
         <v>45825</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76557,7 +76557,7 @@
         <v>45824</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76630,7 +76630,7 @@
         <v>45824</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76703,7 +76703,7 @@
         <v>45826</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76776,7 +76776,7 @@
         <v>45833</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76849,7 +76849,7 @@
         <v>45833</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76922,7 +76922,7 @@
         <v>45833</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76995,7 +76995,7 @@
         <v>45833</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77068,7 +77068,7 @@
         <v>45833</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77141,7 +77141,7 @@
         <v>45833</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77214,7 +77214,7 @@
         <v>45835</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77292,7 +77292,7 @@
         <v>45835</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77370,7 +77370,7 @@
         <v>45833</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77443,7 +77443,7 @@
         <v>45840</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77516,7 +77516,7 @@
         <v>45840</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77594,7 +77594,7 @@
         <v>45202</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77667,7 +77667,7 @@
         <v>45733</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77740,7 +77740,7 @@
         <v>45847</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77818,7 +77818,7 @@
         <v>45849</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77896,7 +77896,7 @@
         <v>45849</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77974,7 +77974,7 @@
         <v>45853</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78047,7 +78047,7 @@
         <v>45855</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78125,7 +78125,7 @@
         <v>45776</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78198,7 +78198,7 @@
         <v>44680</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78271,7 +78271,7 @@
         <v>45862</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78344,7 +78344,7 @@
         <v>45862</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78417,7 +78417,7 @@
         <v>45803</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78490,7 +78490,7 @@
         <v>45874</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78568,7 +78568,7 @@
         <v>45393</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78641,7 +78641,7 @@
         <v>45874</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78719,7 +78719,7 @@
         <v>45877</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78792,7 +78792,7 @@
         <v>45877</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78865,7 +78865,7 @@
         <v>45881</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78938,7 +78938,7 @@
         <v>45882</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79011,7 +79011,7 @@
         <v>45881</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79084,7 +79084,7 @@
         <v>45883</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79157,7 +79157,7 @@
         <v>44160</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79230,7 +79230,7 @@
         <v>44174</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79303,7 +79303,7 @@
         <v>45730</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79376,7 +79376,7 @@
         <v>45405</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79454,7 +79454,7 @@
         <v>45351</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79532,7 +79532,7 @@
         <v>45105</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79605,7 +79605,7 @@
         <v>45699</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79683,7 +79683,7 @@
         <v>45125</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79756,7 +79756,7 @@
         <v>45135</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79829,7 +79829,7 @@
         <v>44769</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79902,7 +79902,7 @@
         <v>44909</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79975,7 +79975,7 @@
         <v>45708</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80053,7 +80053,7 @@
         <v>45761</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80131,7 +80131,7 @@
         <v>45761</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80209,7 +80209,7 @@
         <v>45771</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80287,7 +80287,7 @@
         <v>45814</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80365,7 +80365,7 @@
         <v>45183</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80438,7 +80438,7 @@
         <v>46056</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80511,7 +80511,7 @@
         <v>46072</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80589,7 +80589,7 @@
         <v>46089</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80667,7 +80667,7 @@
         <v>46141</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80745,7 +80745,7 @@
         <v>46198</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45393</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45764</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>46066</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>44572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44911</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46052</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45534</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45230</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45377</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44529</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>45771</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45831</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45845</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>45033</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45077</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>46274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45665</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45008</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44470</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45411</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45524</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45894</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46042</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45926</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46090</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45426</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45321</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>46127</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46135</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46027</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44511</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45985</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>46036</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45841</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45194</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45359</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>46265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45231</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46231</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>46276</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>46276</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46287</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45243</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45490</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44497</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44749</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44470</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44638</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44470</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44795</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44824</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>44804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>44833</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44565</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44484</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44469</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44477</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44692</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44774</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44862</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44762</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44551</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44533</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44839</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44484</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44544</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44797</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>44552</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44559</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44841</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44679</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44537</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44537</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44795</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44578</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44748</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44511</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44798</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45329</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44475</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44806</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44775</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44775</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44866</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45330</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45399</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45259</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45453</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44953</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45243</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45299</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45420</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44928</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44790</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45071</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45516</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44517</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44819</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45793</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45231</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45231</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45796</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45478</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45310</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45533</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44818</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45097</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45436</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46027</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>46027</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46027</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44529</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45884</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46030</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45793</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45546</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45883</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46033</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>46033</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45236</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45337</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45483</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45537</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46027</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>46036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45894</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46042</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46042</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46042</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44890</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45895</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46038</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46042</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>46044</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44914</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>46048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45551</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45582</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46048</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45518</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45518</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45903</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45905</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45905</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45908</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45910</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45910</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45799</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45755</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>46056</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>46057</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45525</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45525</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45618</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46062</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46062</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46062</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45916</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45803</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>46064</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>46064</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45516</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45373</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>46063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>46066</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>46066</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46065</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45920</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45555</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>46070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45923</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46069</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45923</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45923</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45925</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45321</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45925</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45925</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>46072</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46073</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>46073</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>46072</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45201</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45653</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>46078</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45930</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45930</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45243</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45603</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44893</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45623</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>46085</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>46085</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>46086</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>46068</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>46090</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46090</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44944</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46070</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45937</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44529</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45757</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45939</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45940</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44977</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44977</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45943</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45943</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46099</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44872</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>46094</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45930</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>46100</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44911</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45628</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>45946</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45321</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>46105</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45397</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>46105</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45182</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45950</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45558</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45562</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46050</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45377</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46106</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45953</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>46107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>46106</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45953</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45954</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45755</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45363</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>46112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45957</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45958</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45958</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45960</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45960</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>45314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>45961</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45307</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45603</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46125</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>45965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>46122</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>46122</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46126</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45965</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45967</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>46127</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45968</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45967</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45967</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45971</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45813</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45972</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45813</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45813</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45974</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45119</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45973</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45107</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45672</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45975</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45596</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45645</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46129</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>45679</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44826</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44728</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>44907</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46134</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45981</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45664</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45925</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45986</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45985</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>45985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45985</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45985</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45986</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>44911</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45986</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45625</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>45987</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45988</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45636</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45989</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45737</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45784</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45615</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>46136</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>46104</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45659</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45994</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45756</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>45379</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45994</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>46037</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45621</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>46000</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>46000</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46063</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45999</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45679</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45939</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>44519</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45999</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45534</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45888</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45916</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45257</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>45817</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>46085</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45840</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46136</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45440</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45021</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>46003</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45925</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45567</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45637</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46042</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45595</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45989</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45820</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45961</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>46027</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45223</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46010</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44823</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>46010</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45943</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>46010</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>46010</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45686</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>46029</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>46009</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45771</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45560</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46139</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46010</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46035</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46033</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45825</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45821</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46050</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45824</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>46048</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46139</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45824</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>46062</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46044</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45267</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>46048</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45776</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>46139</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45810</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44644</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45744</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>45841</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45826</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46048</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45797</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>46083</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46025</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46025</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45825</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45586</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45077</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>46049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45825</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>46019</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46141</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46141</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46083</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45611</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45825</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45799</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>46062</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>46105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45930</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>46141</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45825</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>46141</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>46141</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>46142</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>44641</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>46050</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>46132</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45896</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45957</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>46070</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45071</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45736</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45686</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>46084</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46146</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>44818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45972</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45587</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45968</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>46146</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>46148</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46148</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>46148</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>46148</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>44930</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>46148</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>46149</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45575</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>46085</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>46064</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>45833</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>46106</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>46048</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45575</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>46113</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45833</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45833</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45737</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45833</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45833</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45952</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>46055</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45833</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>46155</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45833</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45835</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>46104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>46105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45106</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45105</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46157</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45251</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45536</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46159</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44804</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46162</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45840</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45840</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45518</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45321</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45167</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45202</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45733</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45398</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45847</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45646</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45849</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>46139</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46105</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46052</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46167</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45849</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>44571</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45853</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>45776</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45251</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44519</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46056</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46105</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>44680</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45520</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45862</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45425</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45862</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>44544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>44997</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>45588</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46175</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46175</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>44889</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45539</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45539</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45537</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45392</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45124</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>46078</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>44991</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45310</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>46178</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45567</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>46178</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>46128</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>46141</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45874</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45596</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>46178</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>45616</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45617</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45632</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>46140</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45264</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55104,7 +55104,7 @@
         <v>45513</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>45176</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45582</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45569</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>46121</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45874</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55552,7 +55552,7 @@
         <v>45968</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45539</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45539</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>46184</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46184</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46189</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45393</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45672</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>44515</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46191</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46190</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>45803</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46191</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>45534</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>46191</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>45600</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>46190</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56881,7 +56881,7 @@
         <v>46191</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>45334</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>46195</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45877</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>46195</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>46195</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>46195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46043</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45877</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45476</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45033</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46197</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>46197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>46140</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>46197</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>46197</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>44562</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45181</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58215,7 +58215,7 @@
         <v>46196</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58288,7 +58288,7 @@
         <v>46196</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46198</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46198</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45168</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>46198</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58668,7 +58668,7 @@
         <v>45881</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45881</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45558</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>45644</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58960,7 +58960,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46203</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45555</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45623</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>46203</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59325,7 +59325,7 @@
         <v>46203</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46203</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45884</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>45351</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46205</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>45677</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45187</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>45737</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45201</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>45217</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>46209</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46206</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>46206</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46208</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45223</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46206</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45686</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45560</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45672</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45666</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>46205</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>44638</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>46211</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>45085</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         <v>44637</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>45225</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>46212</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>46212</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45721</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>44651</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>46212</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45455</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46259</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45176</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45686</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>45253</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45161</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>46261</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>45275</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62290,7 +62290,7 @@
         <v>45772</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>45107</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>46261</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45422</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>46261</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>45168</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>45695</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>44719</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44813</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45693</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>46224</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>44897</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63196,7 +63196,7 @@
         <v>46265</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>46220</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>46265</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>46153</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>46164</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>46265</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63649,7 +63649,7 @@
         <v>45210</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63722,7 +63722,7 @@
         <v>44798</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>45726</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>46108</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45317</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64019,7 +64019,7 @@
         <v>46223</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46223</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         <v>44775</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45173</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>45231</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>45231</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>46274</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45362</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         <v>46274</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64759,7 +64759,7 @@
         <v>46273</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>45321</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>46274</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65066,7 +65066,7 @@
         <v>45072</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65139,7 +65139,7 @@
         <v>46230</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>45358</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>46276</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>46276</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65441,7 +65441,7 @@
         <v>46276</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>46233</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>45736</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65670,7 +65670,7 @@
         <v>46275</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>45588</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>46275</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65899,7 +65899,7 @@
         <v>45097</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65972,7 +65972,7 @@
         <v>46279</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66050,7 +66050,7 @@
         <v>44847</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66123,7 +66123,7 @@
         <v>46279</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>46237</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>46279</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66347,7 +66347,7 @@
         <v>46237</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66425,7 +66425,7 @@
         <v>46280</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>46280</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66576,7 +66576,7 @@
         <v>46237</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66654,7 +66654,7 @@
         <v>46276</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66727,7 +66727,7 @@
         <v>46237</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>45344</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45671</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66951,7 +66951,7 @@
         <v>45093</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>46239</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>46239</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>45537</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45537</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45517</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67394,7 +67394,7 @@
         <v>46283</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>45259</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>44841</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>45547</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45523</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46241</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67842,7 +67842,7 @@
         <v>45539</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>44746</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45282</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>46198</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68139,7 +68139,7 @@
         <v>46216</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>44621</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>46241</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68363,7 +68363,7 @@
         <v>46241</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68441,7 +68441,7 @@
         <v>44964</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68514,7 +68514,7 @@
         <v>46241</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68592,7 +68592,7 @@
         <v>46287</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68670,7 +68670,7 @@
         <v>45555</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>44762</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68816,7 +68816,7 @@
         <v>44602</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68889,7 +68889,7 @@
         <v>44796</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68962,7 +68962,7 @@
         <v>44742</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69035,7 +69035,7 @@
         <v>46244</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>44807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69186,7 +69186,7 @@
         <v>45443</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45302</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>46244</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>45539</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>46171</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>46098</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>46246</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46057</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>44930</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69853,7 +69853,7 @@
         <v>45733</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69926,7 +69926,7 @@
         <v>45264</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69999,7 +69999,7 @@
         <v>46289</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70077,7 +70077,7 @@
         <v>46248</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70155,7 +70155,7 @@
         <v>46248</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70233,7 +70233,7 @@
         <v>46162</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70306,7 +70306,7 @@
         <v>45258</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70379,7 +70379,7 @@
         <v>45266</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70452,7 +70452,7 @@
         <v>45229</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45230</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70598,7 +70598,7 @@
         <v>45245</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70671,7 +70671,7 @@
         <v>45245</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70744,7 +70744,7 @@
         <v>44960</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70817,7 +70817,7 @@
         <v>44882</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70890,7 +70890,7 @@
         <v>45324</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70963,7 +70963,7 @@
         <v>44700</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71036,7 +71036,7 @@
         <v>44684</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71109,7 +71109,7 @@
         <v>45098</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71182,7 +71182,7 @@
         <v>45002</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71255,7 +71255,7 @@
         <v>44746</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71328,7 +71328,7 @@
         <v>45019</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71401,7 +71401,7 @@
         <v>45019</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71474,7 +71474,7 @@
         <v>45194</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71552,7 +71552,7 @@
         <v>45666</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71625,7 +71625,7 @@
         <v>44930</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>44930</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71771,7 +71771,7 @@
         <v>44834</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         <v>45266</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71917,7 +71917,7 @@
         <v>45344</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71990,7 +71990,7 @@
         <v>45245</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45590</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72146,7 +72146,7 @@
         <v>45618</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72219,7 +72219,7 @@
         <v>45155</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72292,7 +72292,7 @@
         <v>45642</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72365,7 +72365,7 @@
         <v>45182</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72438,7 +72438,7 @@
         <v>45349</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45159</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72589,7 +72589,7 @@
         <v>44840</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72662,7 +72662,7 @@
         <v>45321</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45090</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>45586</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45537</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>45544</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>45665</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73110,7 +73110,7 @@
         <v>45412</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73188,7 +73188,7 @@
         <v>44929</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73261,7 +73261,7 @@
         <v>45204</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73334,7 +73334,7 @@
         <v>45243</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73407,7 +73407,7 @@
         <v>44736</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73480,7 +73480,7 @@
         <v>45321</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73553,7 +73553,7 @@
         <v>45198</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73626,7 +73626,7 @@
         <v>45569</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
         <v>45002</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73772,7 +73772,7 @@
         <v>44551</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73845,7 +73845,7 @@
         <v>44747</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73918,7 +73918,7 @@
         <v>44818</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73991,7 +73991,7 @@
         <v>45646</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74064,7 +74064,7 @@
         <v>45194</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74137,7 +74137,7 @@
         <v>45225</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74210,7 +74210,7 @@
         <v>45209</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74288,7 +74288,7 @@
         <v>45174</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>45194</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>45232</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74507,7 +74507,7 @@
         <v>45139</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74580,7 +74580,7 @@
         <v>44875</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74653,7 +74653,7 @@
         <v>45618</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74726,7 +74726,7 @@
         <v>45622</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74799,7 +74799,7 @@
         <v>45513</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>45666</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>45334</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>44939</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>45259</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>45742</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>45297</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75320,7 +75320,7 @@
         <v>45352</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75393,7 +75393,7 @@
         <v>45321</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75466,7 +75466,7 @@
         <v>45775</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>45253</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75617,7 +75617,7 @@
         <v>45588</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75690,7 +75690,7 @@
         <v>45112</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
         <v>45541</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>45625</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75909,7 +75909,7 @@
         <v>45615</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75982,7 +75982,7 @@
         <v>45623</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76055,7 +76055,7 @@
         <v>45432</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76128,7 +76128,7 @@
         <v>45639</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76201,7 +76201,7 @@
         <v>45722</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76274,7 +76274,7 @@
         <v>45671</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76347,7 +76347,7 @@
         <v>45776</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76420,7 +76420,7 @@
         <v>45776</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76493,7 +76493,7 @@
         <v>45779</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76571,7 +76571,7 @@
         <v>45782</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76644,7 +76644,7 @@
         <v>45782</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76717,7 +76717,7 @@
         <v>45279</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76790,7 +76790,7 @@
         <v>45505</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76863,7 +76863,7 @@
         <v>45616</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76936,7 +76936,7 @@
         <v>45702</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77009,7 +77009,7 @@
         <v>45516</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77082,7 +77082,7 @@
         <v>45784</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77155,7 +77155,7 @@
         <v>45273</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77228,7 +77228,7 @@
         <v>45582</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77301,7 +77301,7 @@
         <v>45545</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77374,7 +77374,7 @@
         <v>45602</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77447,7 +77447,7 @@
         <v>45351</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77520,7 +77520,7 @@
         <v>44799</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77598,7 +77598,7 @@
         <v>45428</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77671,7 +77671,7 @@
         <v>45505</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77744,7 +77744,7 @@
         <v>45789</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77817,7 +77817,7 @@
         <v>45790</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77890,7 +77890,7 @@
         <v>45505</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77963,7 +77963,7 @@
         <v>45789</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78036,7 +78036,7 @@
         <v>45791</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78109,7 +78109,7 @@
         <v>45518</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78182,7 +78182,7 @@
         <v>45518</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78255,7 +78255,7 @@
         <v>45740</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78333,7 +78333,7 @@
         <v>45188</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78406,7 +78406,7 @@
         <v>45552</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78479,7 +78479,7 @@
         <v>45730</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78552,7 +78552,7 @@
         <v>44160</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78625,7 +78625,7 @@
         <v>44174</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78698,7 +78698,7 @@
         <v>45405</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78776,7 +78776,7 @@
         <v>45351</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78854,7 +78854,7 @@
         <v>45105</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78927,7 +78927,7 @@
         <v>45699</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79005,7 +79005,7 @@
         <v>45125</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79078,7 +79078,7 @@
         <v>45135</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79151,7 +79151,7 @@
         <v>44769</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79224,7 +79224,7 @@
         <v>44909</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79297,7 +79297,7 @@
         <v>45708</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79375,7 +79375,7 @@
         <v>45761</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79453,7 +79453,7 @@
         <v>45761</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79531,7 +79531,7 @@
         <v>45771</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79609,7 +79609,7 @@
         <v>45814</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79687,7 +79687,7 @@
         <v>45183</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79760,7 +79760,7 @@
         <v>46056</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79833,7 +79833,7 @@
         <v>46072</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79911,7 +79911,7 @@
         <v>46089</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79989,7 +79989,7 @@
         <v>46141</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80067,7 +80067,7 @@
         <v>46198</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>44918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45393</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45764</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>46066</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>44572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44911</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45973</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45986</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46052</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45534</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45230</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45377</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44529</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>45771</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45831</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45845</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>45033</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45077</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>46274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45665</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45008</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44470</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45411</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45524</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45894</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46042</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45926</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46090</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45426</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45321</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>46127</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46135</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46027</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44511</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45985</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>46036</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45841</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45194</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45359</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>46265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45231</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46231</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>46276</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>46276</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>46287</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45243</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45784</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45490</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44497</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44749</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44470</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44638</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44470</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44795</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44824</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>44804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>44833</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44565</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44484</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44469</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44477</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44692</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44774</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44862</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44762</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>44551</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44533</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44839</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44484</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44544</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44797</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>44552</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44559</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>44841</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44679</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44537</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44537</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44795</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44578</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44748</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44511</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44798</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45329</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44475</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44806</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>44775</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44775</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44866</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45330</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45399</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45259</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45453</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44953</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45243</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45299</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45420</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44928</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44790</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45071</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45516</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44517</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44819</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45793</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45231</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45231</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45796</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45478</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45310</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45533</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44818</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45097</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45436</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46027</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>46027</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46027</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44529</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45884</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46030</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45793</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45546</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45883</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46033</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>46033</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45236</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45337</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45483</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45537</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46027</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>46036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>46036</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45894</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46042</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46042</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46042</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44890</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45895</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46038</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46042</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>46044</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44914</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>46048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45551</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45582</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46048</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45518</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45518</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45903</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45905</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45905</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45908</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45910</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45910</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45799</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45755</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>46056</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>46057</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45525</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45525</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45618</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46062</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46062</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46062</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45916</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45803</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>46064</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>46064</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45516</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45373</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>46063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>46066</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>46066</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46065</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45920</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45555</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>46070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45923</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46069</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45923</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45923</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45925</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45321</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45925</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45925</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>46072</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46073</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>46073</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>46072</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45201</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45653</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>46078</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45930</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45930</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45243</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45603</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44893</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45623</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>46085</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>46085</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>46086</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>46068</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>46090</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46090</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44944</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46070</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45937</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44529</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45757</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45939</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45940</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44977</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44977</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45943</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45943</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46099</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44872</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>46094</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45930</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>46100</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44911</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45628</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>45946</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45321</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>46105</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45397</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>46105</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45182</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45950</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45558</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>46106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45562</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46050</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45377</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46106</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45953</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>46107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>46106</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45953</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45954</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45755</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45363</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>46112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45957</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45958</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45958</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45960</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45960</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>45314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>45961</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45307</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45603</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46125</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>45965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>46122</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>46122</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46126</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45965</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45967</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>46127</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45968</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45967</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45967</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45971</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45813</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45972</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45813</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45813</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45974</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45119</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45973</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45107</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45672</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45975</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45596</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45645</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46129</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>45679</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44826</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44728</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>44907</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46134</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45981</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45664</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45925</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45986</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45985</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>45985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45985</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45985</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45986</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>44911</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45986</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45625</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>45987</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45988</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45636</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45989</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45737</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45784</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45615</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>46136</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>46104</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45659</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45994</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45756</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>45379</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45994</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>46037</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45621</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>46000</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>46000</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46063</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45481</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45999</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45679</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45939</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>44519</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45999</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45534</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45888</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45916</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45257</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>45817</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>46085</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45840</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46136</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45440</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45021</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>46003</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45925</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45567</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45637</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46042</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45595</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45989</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45820</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45819</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45961</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>46027</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45223</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46010</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44823</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>46010</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45943</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>46010</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>46010</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45686</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>46029</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>46009</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45771</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45560</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46139</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46010</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46035</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46033</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>45825</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45821</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46050</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45824</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>46048</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46139</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45824</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>46062</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46044</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45267</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>46048</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45776</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>46139</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45810</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44644</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45744</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>45841</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45826</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46048</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45797</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>46083</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46025</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46025</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45825</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45586</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45077</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>46049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45825</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>46019</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46141</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46141</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46083</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45611</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45825</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45799</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>46062</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>46105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45930</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>46141</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45825</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>46141</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>46141</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>46142</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>44641</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>46050</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>46132</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45896</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45957</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>46070</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45071</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45736</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45686</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>46084</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46146</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>44818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45972</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45587</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45968</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>46146</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>46148</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46148</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>46148</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>46148</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>44930</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>46148</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>46149</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45575</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>46085</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>46064</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>45833</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>46106</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>46048</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45575</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>46113</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45833</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45833</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45737</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45833</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45833</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45952</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>46055</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45833</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>46155</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45833</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45835</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>46104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>46105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45106</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45105</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46157</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45251</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45536</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46159</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>44804</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46162</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45840</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45840</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45518</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45321</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45167</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45202</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45733</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45398</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45847</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45646</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45849</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>46139</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>46105</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46052</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46167</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45849</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>44571</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45853</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>45776</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45251</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44519</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46056</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46105</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>44680</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45520</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45862</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45425</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45862</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>44544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>44997</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>45588</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46175</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46175</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>44889</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45539</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45539</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45537</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45392</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45124</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>46078</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>44991</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45310</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>46178</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45567</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>46178</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>46128</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>46141</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45874</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45596</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>46178</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>45616</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45617</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45632</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>46140</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45264</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55104,7 +55104,7 @@
         <v>45513</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>45176</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45582</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45569</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>46121</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45874</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55552,7 +55552,7 @@
         <v>45968</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45539</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45539</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>46184</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46184</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46189</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45393</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45672</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>44515</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46191</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46190</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>45803</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46191</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>45534</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>46191</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>45600</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>46190</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56881,7 +56881,7 @@
         <v>46191</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>45334</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>46195</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45877</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>46195</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>46195</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>46195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46043</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45877</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45476</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45033</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46197</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>46197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>46140</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>46197</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>46197</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>44562</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45181</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58215,7 +58215,7 @@
         <v>46196</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58288,7 +58288,7 @@
         <v>46196</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46198</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46198</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45168</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>46198</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58668,7 +58668,7 @@
         <v>45881</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45881</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45558</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>45644</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58960,7 +58960,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46203</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45555</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45623</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>46203</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59325,7 +59325,7 @@
         <v>46203</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46203</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45884</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>45351</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46205</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>45677</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45187</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>45737</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45201</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>45217</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>46209</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46206</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>46206</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46208</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45223</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46206</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45686</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45560</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45672</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45666</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>46205</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>44638</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>46211</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>45085</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         <v>44637</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>45225</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>46212</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>46212</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45721</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>44651</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>46212</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45455</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46259</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45176</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61920,7 +61920,7 @@
         <v>45686</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>45253</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45161</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>46261</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>45275</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62290,7 +62290,7 @@
         <v>45772</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>45107</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>46261</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45422</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>46261</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>45168</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>45695</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>44719</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44813</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45693</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>46224</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>44897</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63196,7 +63196,7 @@
         <v>46265</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>46220</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>46265</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>46153</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>46164</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>46265</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63649,7 +63649,7 @@
         <v>45210</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63722,7 +63722,7 @@
         <v>44798</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>45726</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>46108</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45317</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64019,7 +64019,7 @@
         <v>46223</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46223</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         <v>44775</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45173</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>45231</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>45231</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>46274</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45362</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         <v>46274</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64759,7 +64759,7 @@
         <v>46273</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>45321</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>46274</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65066,7 +65066,7 @@
         <v>45072</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65139,7 +65139,7 @@
         <v>46230</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>45358</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>46276</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>46276</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65441,7 +65441,7 @@
         <v>46276</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>46233</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>45736</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65670,7 +65670,7 @@
         <v>46275</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>45588</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>46275</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65899,7 +65899,7 @@
         <v>45097</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65972,7 +65972,7 @@
         <v>46279</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66050,7 +66050,7 @@
         <v>44847</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66123,7 +66123,7 @@
         <v>46279</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>46237</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>46279</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66347,7 +66347,7 @@
         <v>46237</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66425,7 +66425,7 @@
         <v>46280</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>46280</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66576,7 +66576,7 @@
         <v>46237</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66654,7 +66654,7 @@
         <v>46276</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66727,7 +66727,7 @@
         <v>46237</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>45344</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45671</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66951,7 +66951,7 @@
         <v>45093</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>46239</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>46239</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>45537</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>45537</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45517</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67394,7 +67394,7 @@
         <v>46283</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>45259</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>44841</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>45547</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45523</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>46241</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67842,7 +67842,7 @@
         <v>45539</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67915,7 +67915,7 @@
         <v>44746</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67988,7 +67988,7 @@
         <v>45282</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>46198</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68139,7 +68139,7 @@
         <v>46216</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>44621</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>46241</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68363,7 +68363,7 @@
         <v>46241</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68441,7 +68441,7 @@
         <v>44964</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68514,7 +68514,7 @@
         <v>46241</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68592,7 +68592,7 @@
         <v>46287</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68670,7 +68670,7 @@
         <v>45555</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>44762</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68816,7 +68816,7 @@
         <v>44602</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68889,7 +68889,7 @@
         <v>44796</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68962,7 +68962,7 @@
         <v>44742</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69035,7 +69035,7 @@
         <v>46244</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>44807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69186,7 +69186,7 @@
         <v>45443</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45302</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>46244</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>45539</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>46171</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>46098</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>46246</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46057</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>44930</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69853,7 +69853,7 @@
         <v>45733</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69926,7 +69926,7 @@
         <v>45264</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69999,7 +69999,7 @@
         <v>46289</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70077,7 +70077,7 @@
         <v>46248</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70155,7 +70155,7 @@
         <v>46248</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70233,7 +70233,7 @@
         <v>46162</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70306,7 +70306,7 @@
         <v>45258</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70379,7 +70379,7 @@
         <v>45266</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70452,7 +70452,7 @@
         <v>45229</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45230</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70598,7 +70598,7 @@
         <v>45245</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70671,7 +70671,7 @@
         <v>45245</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70744,7 +70744,7 @@
         <v>44960</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70817,7 +70817,7 @@
         <v>44882</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70890,7 +70890,7 @@
         <v>45324</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70963,7 +70963,7 @@
         <v>44700</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71036,7 +71036,7 @@
         <v>44684</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71109,7 +71109,7 @@
         <v>45098</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71182,7 +71182,7 @@
         <v>45002</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71255,7 +71255,7 @@
         <v>44746</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71328,7 +71328,7 @@
         <v>45019</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71401,7 +71401,7 @@
         <v>45019</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71474,7 +71474,7 @@
         <v>45194</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71552,7 +71552,7 @@
         <v>45666</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71625,7 +71625,7 @@
         <v>44930</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>44930</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71771,7 +71771,7 @@
         <v>44834</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         <v>45266</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71917,7 +71917,7 @@
         <v>45344</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71990,7 +71990,7 @@
         <v>45245</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45590</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72146,7 +72146,7 @@
         <v>45618</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72219,7 +72219,7 @@
         <v>45155</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72292,7 +72292,7 @@
         <v>45642</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72365,7 +72365,7 @@
         <v>45182</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72438,7 +72438,7 @@
         <v>45349</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45159</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72589,7 +72589,7 @@
         <v>44840</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72662,7 +72662,7 @@
         <v>45321</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45090</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>45586</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45537</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>45544</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>45665</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73110,7 +73110,7 @@
         <v>45412</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73188,7 +73188,7 @@
         <v>44929</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73261,7 +73261,7 @@
         <v>45204</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73334,7 +73334,7 @@
         <v>45243</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73407,7 +73407,7 @@
         <v>44736</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73480,7 +73480,7 @@
         <v>45321</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73553,7 +73553,7 @@
         <v>45198</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73626,7 +73626,7 @@
         <v>45569</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
         <v>45002</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73772,7 +73772,7 @@
         <v>44551</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73845,7 +73845,7 @@
         <v>44747</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73918,7 +73918,7 @@
         <v>44818</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73991,7 +73991,7 @@
         <v>45646</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74064,7 +74064,7 @@
         <v>45194</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74137,7 +74137,7 @@
         <v>45225</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74210,7 +74210,7 @@
         <v>45209</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74288,7 +74288,7 @@
         <v>45174</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>45194</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>45232</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74507,7 +74507,7 @@
         <v>45139</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74580,7 +74580,7 @@
         <v>44875</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74653,7 +74653,7 @@
         <v>45618</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74726,7 +74726,7 @@
         <v>45622</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74799,7 +74799,7 @@
         <v>45513</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>45666</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>45334</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>44939</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>45259</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>45742</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>45297</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75320,7 +75320,7 @@
         <v>45352</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75393,7 +75393,7 @@
         <v>45321</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75466,7 +75466,7 @@
         <v>45775</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>45253</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75617,7 +75617,7 @@
         <v>45588</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75690,7 +75690,7 @@
         <v>45112</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
         <v>45541</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>45625</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75909,7 +75909,7 @@
         <v>45615</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75982,7 +75982,7 @@
         <v>45623</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76055,7 +76055,7 @@
         <v>45432</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76128,7 +76128,7 @@
         <v>45639</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76201,7 +76201,7 @@
         <v>45722</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76274,7 +76274,7 @@
         <v>45671</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76347,7 +76347,7 @@
         <v>45776</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76420,7 +76420,7 @@
         <v>45776</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76493,7 +76493,7 @@
         <v>45779</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76571,7 +76571,7 @@
         <v>45782</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76644,7 +76644,7 @@
         <v>45782</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76717,7 +76717,7 @@
         <v>45279</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76790,7 +76790,7 @@
         <v>45505</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76863,7 +76863,7 @@
         <v>45616</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76936,7 +76936,7 @@
         <v>45702</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77009,7 +77009,7 @@
         <v>45516</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77082,7 +77082,7 @@
         <v>45784</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77155,7 +77155,7 @@
         <v>45273</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77228,7 +77228,7 @@
         <v>45582</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77301,7 +77301,7 @@
         <v>45545</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77374,7 +77374,7 @@
         <v>45602</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77447,7 +77447,7 @@
         <v>45351</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77520,7 +77520,7 @@
         <v>44799</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77598,7 +77598,7 @@
         <v>45428</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77671,7 +77671,7 @@
         <v>45505</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77744,7 +77744,7 @@
         <v>45789</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77817,7 +77817,7 @@
         <v>45790</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77890,7 +77890,7 @@
         <v>45505</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77963,7 +77963,7 @@
         <v>45789</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78036,7 +78036,7 @@
         <v>45791</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78109,7 +78109,7 @@
         <v>45518</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78182,7 +78182,7 @@
         <v>45518</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78255,7 +78255,7 @@
         <v>45740</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78333,7 +78333,7 @@
         <v>45188</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78406,7 +78406,7 @@
         <v>45552</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78479,7 +78479,7 @@
         <v>45730</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78552,7 +78552,7 @@
         <v>44160</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78625,7 +78625,7 @@
         <v>44174</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78698,7 +78698,7 @@
         <v>45405</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78776,7 +78776,7 @@
         <v>45351</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78854,7 +78854,7 @@
         <v>45105</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78927,7 +78927,7 @@
         <v>45699</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79005,7 +79005,7 @@
         <v>45125</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79078,7 +79078,7 @@
         <v>45135</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79151,7 +79151,7 @@
         <v>44769</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79224,7 +79224,7 @@
         <v>44909</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79297,7 +79297,7 @@
         <v>45708</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79375,7 +79375,7 @@
         <v>45761</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79453,7 +79453,7 @@
         <v>45761</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79531,7 +79531,7 @@
         <v>45771</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79609,7 +79609,7 @@
         <v>45814</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79687,7 +79687,7 @@
         <v>45183</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79760,7 +79760,7 @@
         <v>46056</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79833,7 +79833,7 @@
         <v>46072</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79911,7 +79911,7 @@
         <v>46089</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79989,7 +79989,7 @@
         <v>46141</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80067,7 +80067,7 @@
         <v>46198</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>46105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45764</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46066</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45996</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45476</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45230</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44911</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45222</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>45033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45845</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45771</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45377</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45406</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46297</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45490</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45321</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>45525</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45894</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45279</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46042</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45524</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45194</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45926</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>46090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45961</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45359</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>46135</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44511</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>46155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>46265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45243</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>46276</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>46276</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>46287</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45411</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45365</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45784</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44497</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44749</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44638</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44740</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44790</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44795</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44795</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44565</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44733</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44484</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44571</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44477</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44692</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44774</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44838</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44727</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44862</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>44638</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44762</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>44551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44845</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>44484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44839</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44839</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44679</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44579</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44732</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44795</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44578</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44537</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44537</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44748</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45321</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45432</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45672</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44930</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44651</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45636</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45523</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44826</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45555</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44893</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45093</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44602</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45517</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45671</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45351</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45344</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44977</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45505</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45582</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45702</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45299</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45505</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45428</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45516</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45789</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45789</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>46003</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45884</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45201</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45478</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45558</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45321</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45344</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45518</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45736</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45539</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45552</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45925</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45243</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44747</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45677</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>46010</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>46010</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46010</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45363</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45790</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45321</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45888</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45253</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45958</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45700</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46027</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>46027</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>46027</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46027</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45188</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>44889</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44872</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44991</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45173</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45518</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45898</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46031</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45398</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>46030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>46033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45740</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46033</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45903</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46027</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46033</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45902</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>46036</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45352</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46036</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>46036</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45793</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45905</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45793</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45194</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45513</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45755</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46042</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45910</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45910</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45097</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45594</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>46042</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>46042</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45796</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45533</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45915</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46049</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45453</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45796</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45916</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45798</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46050</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45373</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45803</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45803</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45755</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45919</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45920</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45300</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45243</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45923</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45923</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45201</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45923</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45925</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46056</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46057</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45925</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45925</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45930</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44882</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45930</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46063</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46062</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45653</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46062</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46062</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>44736</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45933</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45603</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45229</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46064</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46064</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46065</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45562</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45547</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46066</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46066</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45337</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>46066</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45937</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45937</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45033</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45937</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45539</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45939</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45002</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45223</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>46072</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46072</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45943</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45275</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45943</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45940</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45943</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45544</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45930</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45412</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46078</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45757</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45085</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45628</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45245</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45377</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45950</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45953</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45168</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45813</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45953</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45954</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>46085</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46085</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>46068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46086</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>46090</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>46090</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45813</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45958</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45251</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45960</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>46070</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45019</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45960</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45019</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>45965</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45817</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45967</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45967</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45966</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45310</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45971</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>46094</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45266</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45971</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45968</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45972</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>46100</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>46099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>44621</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45973</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>46098</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46099</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45253</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45974</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>44944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>44834</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45666</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45974</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45974</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45975</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46104</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46105</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>46105</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>46106</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>46106</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45679</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45513</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46105</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46107</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45671</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45686</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45819</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45155</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45645</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45985</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45821</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45985</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45820</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44911</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45985</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45985</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46112</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45985</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45985</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45985</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45986</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45615</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45825</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45825</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45986</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45596</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45988</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45989</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45825</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45989</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46122</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45824</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45824</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45992</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45618</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46122</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44798</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46126</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46126</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>46125</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45659</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45106</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45826</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44529</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45994</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45264</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45994</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45999</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45726</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45999</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45181</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46129</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>46127</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46000</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44911</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>46133</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46000</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46000</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>45259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45833</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45637</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45833</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45833</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45124</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45314</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45077</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45833</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>45833</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45833</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45588</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45569</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45835</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45835</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45297</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45539</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>46136</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45321</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45833</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45595</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46029</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45590</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45225</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>46136</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45209</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45534</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45257</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45888</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46025</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46139</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45840</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45840</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45810</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46029</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45202</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44796</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45737</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46033</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45943</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45733</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45481</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45358</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45961</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45621</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45679</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45586</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46050</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45560</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45847</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44928</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45849</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45849</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46139</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45776</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45797</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>44515</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>46050</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45853</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44641</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>46049</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45841</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45266</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45916</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45776</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>46139</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>44684</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45539</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45259</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>44977</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45569</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45537</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>45686</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>45825</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45989</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>44897</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>46139</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44762</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45784</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>44680</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45334</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45379</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45623</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>46104</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>46035</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45925</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45539</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46083</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>45611</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46036</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>46048</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45957</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>46070</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45440</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>46085</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46062</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45646</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>46025</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45862</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45799</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45862</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>46050</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46042</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46057</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45567</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46084</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>44529</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45330</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46083</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46132</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45251</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>46141</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46141</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45672</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46048</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46141</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45245</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46019</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45541</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45721</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45896</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>46037</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45167</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46063</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>46044</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45520</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>44840</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45107</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>44964</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>44644</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45939</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46141</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45537</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46062</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45930</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>46141</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45686</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46027</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46142</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45972</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>45537</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45616</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>45968</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46052</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46146</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46146</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>46148</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>46148</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46149</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46148</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>46148</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54296,7 +54296,7 @@
         <v>45803</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46148</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45742</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45952</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>46085</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54671,7 +54671,7 @@
         <v>45575</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>44746</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>44914</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>44960</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>46064</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55041,7 +55041,7 @@
         <v>46106</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>46113</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45737</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>46105</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45397</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45264</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         <v>46104</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>46155</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45267</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>46048</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>46055</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55937,7 +55937,7 @@
         <v>46157</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45321</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>44562</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56156,7 +56156,7 @@
         <v>45176</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>45874</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45393</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45695</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45161</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45874</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>46162</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44807</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>46167</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>45877</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>45264</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45877</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45603</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45646</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45324</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>46105</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
         <v>46052</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>46056</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>46139</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57558,7 +57558,7 @@
         <v>46105</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45588</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>45881</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45882</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57860,7 +57860,7 @@
         <v>45881</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45883</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45632</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58079,7 +58079,7 @@
         <v>46175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>46175</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>45071</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>46178</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>46141</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>44939</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>46078</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46178</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45622</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>46140</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>45617</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45639</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>46121</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>44519</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59189,7 +59189,7 @@
         <v>45536</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46184</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>46184</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45968</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45159</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46190</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>46190</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>46189</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45737</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>46191</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45672</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60012,7 +60012,7 @@
         <v>46043</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>46191</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60158,7 +60158,7 @@
         <v>46191</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60231,7 +60231,7 @@
         <v>46191</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         <v>45546</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45267</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>46196</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>46195</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45615</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>46195</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>46196</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>45107</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>45107</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>46195</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61044,7 +61044,7 @@
         <v>46195</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45090</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>44823</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>44813</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>45310</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>46198</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44775</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>46198</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>46197</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45551</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>46197</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45443</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>46197</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>45307</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>46140</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46198</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>46197</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45282</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>46203</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>46203</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>46203</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45665</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44638</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>46206</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>46208</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>46205</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>46206</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>46209</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63196,7 +63196,7 @@
         <v>44775</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63269,7 +63269,7 @@
         <v>44775</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63342,7 +63342,7 @@
         <v>46205</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>44798</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46212</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>46211</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46212</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>46212</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>44544</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>45625</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45436</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>45587</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>46259</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45618</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46258</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>45198</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>44790</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>46261</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64545,7 +64545,7 @@
         <v>46261</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64623,7 +64623,7 @@
         <v>45302</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64696,7 +64696,7 @@
         <v>44818</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>46261</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64842,7 +64842,7 @@
         <v>45097</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>46265</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45399</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45618</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45558</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>46265</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>46153</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>46164</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>46220</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45693</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>46265</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>46108</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45772</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>46223</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>46223</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44953</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>46224</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45217</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45321</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45518</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45518</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45072</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>44700</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45593</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>44818</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46273</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>46230</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>45105</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66921,7 +66921,7 @@
         <v>46274</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>46275</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>46274</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>46275</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>46274</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>46233</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46276</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>46279</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>46279</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>46276</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67696,7 +67696,7 @@
         <v>46279</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46276</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>45168</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46237</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68003,7 +68003,7 @@
         <v>45671</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68076,7 +68076,7 @@
         <v>45672</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>45176</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>46276</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45420</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>46280</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68446,7 +68446,7 @@
         <v>46237</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>45555</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68597,7 +68597,7 @@
         <v>44910</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68670,7 +68670,7 @@
         <v>46237</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>46280</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>46237</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68899,7 +68899,7 @@
         <v>45236</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>45722</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>45590</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69123,7 +69123,7 @@
         <v>45483</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>46239</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>45210</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>44571</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>45230</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69566,7 +69566,7 @@
         <v>45243</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69639,7 +69639,7 @@
         <v>45537</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69712,7 +69712,7 @@
         <v>46241</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69790,7 +69790,7 @@
         <v>46241</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>46198</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69946,7 +69946,7 @@
         <v>44939</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>44728</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70097,7 +70097,7 @@
         <v>45575</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70175,7 +70175,7 @@
         <v>46241</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70253,7 +70253,7 @@
         <v>44818</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70326,7 +70326,7 @@
         <v>46216</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70399,7 +70399,7 @@
         <v>46244</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70477,7 +70477,7 @@
         <v>46287</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70555,7 +70555,7 @@
         <v>45317</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70628,7 +70628,7 @@
         <v>44929</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70701,7 +70701,7 @@
         <v>46244</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>45644</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>46241</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>46246</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46289</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71081,7 +71081,7 @@
         <v>46057</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71154,7 +71154,7 @@
         <v>46248</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71232,7 +71232,7 @@
         <v>45476</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71305,7 +71305,7 @@
         <v>46171</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71383,7 +71383,7 @@
         <v>45642</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71456,7 +71456,7 @@
         <v>44637</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71529,7 +71529,7 @@
         <v>45119</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71602,7 +71602,7 @@
         <v>46248</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71680,7 +71680,7 @@
         <v>45223</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71753,7 +71753,7 @@
         <v>44806</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71826,7 +71826,7 @@
         <v>44519</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71899,7 +71899,7 @@
         <v>44875</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71972,7 +71972,7 @@
         <v>45646</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72045,7 +72045,7 @@
         <v>46239</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72118,7 +72118,7 @@
         <v>45582</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46203</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46293</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72347,7 +72347,7 @@
         <v>44841</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72420,7 +72420,7 @@
         <v>45775</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72498,7 +72498,7 @@
         <v>45098</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72571,7 +72571,7 @@
         <v>45567</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72644,7 +72644,7 @@
         <v>45182</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72717,7 +72717,7 @@
         <v>46098</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         <v>45194</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>45187</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>45072</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73019,7 +73019,7 @@
         <v>46162</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>45329</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>45204</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73238,7 +73238,7 @@
         <v>45516</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>45946</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73389,7 +73389,7 @@
         <v>46296</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>46296</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73545,7 +73545,7 @@
         <v>45194</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73618,7 +73618,7 @@
         <v>46159</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73696,7 +73696,7 @@
         <v>45349</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>45245</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73842,7 +73842,7 @@
         <v>44847</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73915,7 +73915,7 @@
         <v>45071</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73988,7 +73988,7 @@
         <v>46134</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74066,7 +74066,7 @@
         <v>45736</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74139,7 +74139,7 @@
         <v>46296</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74217,7 +74217,7 @@
         <v>46297</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74295,7 +74295,7 @@
         <v>46297</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74368,7 +74368,7 @@
         <v>45455</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74446,7 +74446,7 @@
         <v>44930</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74519,7 +74519,7 @@
         <v>44517</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>45139</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74665,7 +74665,7 @@
         <v>45231</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74738,7 +74738,7 @@
         <v>45231</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74811,7 +74811,7 @@
         <v>45534</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74884,7 +74884,7 @@
         <v>45392</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74957,7 +74957,7 @@
         <v>44997</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75030,7 +75030,7 @@
         <v>45002</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75103,7 +75103,7 @@
         <v>45259</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75176,7 +75176,7 @@
         <v>45625</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75249,7 +75249,7 @@
         <v>44746</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>45600</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
         <v>45232</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75468,7 +75468,7 @@
         <v>45756</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75541,7 +75541,7 @@
         <v>44907</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75619,7 +75619,7 @@
         <v>45582</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75692,7 +75692,7 @@
         <v>45744</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75765,7 +75765,7 @@
         <v>45190</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75838,7 +75838,7 @@
         <v>45176</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75916,7 +75916,7 @@
         <v>44866</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75989,7 +75989,7 @@
         <v>45422</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76067,7 +76067,7 @@
         <v>45516</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76140,7 +76140,7 @@
         <v>45112</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76213,7 +76213,7 @@
         <v>45334</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76286,7 +76286,7 @@
         <v>45173</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76359,7 +76359,7 @@
         <v>45586</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76437,7 +76437,7 @@
         <v>45733</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76510,7 +76510,7 @@
         <v>45525</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76583,7 +76583,7 @@
         <v>45525</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76656,7 +76656,7 @@
         <v>44551</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76729,7 +76729,7 @@
         <v>45321</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76802,7 +76802,7 @@
         <v>44804</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>45686</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45666</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77021,7 +77021,7 @@
         <v>44475</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77094,7 +77094,7 @@
         <v>45771</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77167,7 +77167,7 @@
         <v>45112</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77240,7 +77240,7 @@
         <v>45188</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77313,7 +77313,7 @@
         <v>45560</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77386,7 +77386,7 @@
         <v>45666</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77459,7 +77459,7 @@
         <v>45776</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77532,7 +77532,7 @@
         <v>45776</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>45779</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>45616</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>45782</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45279</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>45505</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>45782</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78048,7 +78048,7 @@
         <v>44799</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78126,7 +78126,7 @@
         <v>45602</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>45784</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78272,7 +78272,7 @@
         <v>45351</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78345,7 +78345,7 @@
         <v>45545</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78418,7 +78418,7 @@
         <v>45273</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78491,7 +78491,7 @@
         <v>44160</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78564,7 +78564,7 @@
         <v>44174</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78637,7 +78637,7 @@
         <v>45730</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78710,7 +78710,7 @@
         <v>45405</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78788,7 +78788,7 @@
         <v>45351</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78866,7 +78866,7 @@
         <v>45105</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78939,7 +78939,7 @@
         <v>45699</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79017,7 +79017,7 @@
         <v>45125</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79090,7 +79090,7 @@
         <v>45135</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79163,7 +79163,7 @@
         <v>44769</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79236,7 +79236,7 @@
         <v>44909</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79309,7 +79309,7 @@
         <v>45708</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79387,7 +79387,7 @@
         <v>45761</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79465,7 +79465,7 @@
         <v>45761</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79543,7 +79543,7 @@
         <v>45771</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79621,7 +79621,7 @@
         <v>45814</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79699,7 +79699,7 @@
         <v>45183</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79772,7 +79772,7 @@
         <v>46056</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79845,7 +79845,7 @@
         <v>46072</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79923,7 +79923,7 @@
         <v>46089</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80001,7 +80001,7 @@
         <v>46141</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80079,7 +80079,7 @@
         <v>46198</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44818</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44874</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>46105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45764</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46066</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45996</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46036</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45476</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45230</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44911</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45222</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>45033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45845</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45771</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45377</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45406</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46297</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45490</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45321</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>45525</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45894</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45279</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46042</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45524</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45194</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45926</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>46090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45961</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45359</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>46135</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44511</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>46155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>46265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45243</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>46276</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>46276</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>46287</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45411</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45365</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45784</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44497</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44749</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44638</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44740</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44790</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44795</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44795</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44565</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44733</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44484</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44571</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44477</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44692</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44774</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44838</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44727</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44862</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>44638</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44762</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>44551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44845</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>44484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44839</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44839</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44679</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44579</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44732</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44795</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44578</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44537</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44537</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44748</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45321</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45432</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45672</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44930</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44651</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45636</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45523</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44826</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45555</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44893</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45093</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44602</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45517</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45671</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45351</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45344</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44977</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45505</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45582</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45702</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45299</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45505</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45428</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45516</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45789</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45789</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>46003</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45884</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45201</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45478</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45558</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45321</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45344</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45518</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45736</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45539</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45552</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45925</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45243</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44747</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45225</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45677</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>46010</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>46010</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46010</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45363</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45790</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45321</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45888</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45253</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45958</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45700</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46027</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>46027</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>46027</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46027</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45188</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>44889</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44872</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44991</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45173</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45518</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45898</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46031</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45398</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>46030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>46033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45740</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46033</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45903</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46027</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46033</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45902</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>46036</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45352</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46036</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>46036</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45793</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45905</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45793</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45097</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45194</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45513</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45755</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46042</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>46038</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45910</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45910</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45097</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45594</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>46042</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>46042</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45796</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45533</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45915</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46049</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45453</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45796</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45916</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45798</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46050</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45373</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45803</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45803</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45755</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45919</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45920</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45300</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45243</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45923</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45923</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45201</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45923</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45925</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46056</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46057</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45925</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45925</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45930</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44882</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45930</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46063</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46062</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45653</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46062</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46062</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>44736</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45933</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45603</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45229</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46064</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46064</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46065</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45562</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45547</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46066</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46066</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45337</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>46066</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45937</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45937</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45033</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45937</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45539</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45939</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45002</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45223</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>46072</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46072</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45939</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45943</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45275</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45943</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45940</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45940</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45943</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45544</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45930</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45412</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46078</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45757</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45085</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45628</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45245</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45377</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45950</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45953</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45168</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45813</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45953</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45954</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>46085</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46085</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>46068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46086</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>46090</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>46090</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45813</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45958</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45251</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45960</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>46070</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45019</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45960</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45019</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>45965</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45817</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45967</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45967</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45966</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45310</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45971</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>46094</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45266</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45971</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45968</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45972</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>46100</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>46099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>44621</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45973</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>46098</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46099</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45253</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45974</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>44944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>44834</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45666</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45974</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45974</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45975</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46104</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46105</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>46105</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>46106</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>46106</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45679</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45513</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46105</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46107</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45671</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45686</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45819</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45155</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45645</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45985</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45821</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45985</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45820</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44911</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45985</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45985</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46112</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45985</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45985</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45985</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45986</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45615</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45825</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45825</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45986</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45596</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45988</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45989</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45825</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45989</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46122</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45824</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45824</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45992</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45618</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46122</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44798</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46126</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46126</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>46125</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45659</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45106</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45826</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44529</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45994</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45264</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45994</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45999</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45726</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45999</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45181</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46129</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>46127</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46000</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44911</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>46133</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46000</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46000</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>45259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45833</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45637</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45833</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45833</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45124</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45314</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45077</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45833</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>45833</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45833</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45588</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45569</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45835</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45835</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45297</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45539</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>46136</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45321</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45833</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45595</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46029</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45590</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45225</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>46136</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45209</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45534</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45257</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45888</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46025</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46139</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45840</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45840</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45810</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46029</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45202</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44796</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45737</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46033</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45943</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45733</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45481</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45358</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45961</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45621</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45679</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45586</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46050</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45560</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45847</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44928</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45849</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45849</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46139</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45776</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45797</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>44515</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>46050</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45853</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44641</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>46049</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45841</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45266</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45916</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45776</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>46139</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>44684</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45539</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45259</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>44977</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45569</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45537</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>45686</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>45825</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45989</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>44897</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>46139</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44762</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45784</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>44680</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45334</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45379</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45623</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>46104</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>46035</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45925</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45539</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46083</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>45611</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46036</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>46048</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45957</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>46070</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45440</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>46085</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46062</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45646</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>46025</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45862</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45799</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45862</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>46050</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46042</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46057</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45567</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46084</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>44529</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45330</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46083</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46132</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45251</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>46141</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46141</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45672</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46048</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46141</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45245</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46019</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45541</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45721</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45896</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>46037</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45167</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46063</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>46044</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45520</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>44840</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45107</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>44964</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>44644</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45939</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46141</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45537</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>46062</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45930</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>46141</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45686</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46027</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46142</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45972</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>45537</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45616</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>45968</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46052</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46146</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46146</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>46148</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>46148</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46149</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46148</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>46148</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54296,7 +54296,7 @@
         <v>45803</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46148</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>45742</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45952</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>46085</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54671,7 +54671,7 @@
         <v>45575</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>44746</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>44914</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>44960</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>46064</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55041,7 +55041,7 @@
         <v>46106</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>46113</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45737</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>46105</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45397</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45264</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         <v>46104</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>46155</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45267</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>46048</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>46055</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55937,7 +55937,7 @@
         <v>46157</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45321</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>44562</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56156,7 +56156,7 @@
         <v>45176</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>45874</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45393</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45695</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45161</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45874</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>46162</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44807</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>46167</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>45877</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>45264</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45877</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45603</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45646</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45324</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>46105</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
         <v>46052</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>46056</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>46139</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57558,7 +57558,7 @@
         <v>46105</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45588</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>45881</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45882</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57860,7 +57860,7 @@
         <v>45881</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45883</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45632</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58079,7 +58079,7 @@
         <v>46175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>46175</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>45071</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>46178</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>46141</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>44939</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>46078</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46178</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45622</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>46140</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>45617</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45639</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>46121</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>44519</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59189,7 +59189,7 @@
         <v>45536</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46184</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>46184</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45968</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45159</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46190</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>46190</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>46189</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45737</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>46191</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45672</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60012,7 +60012,7 @@
         <v>46043</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>46191</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60158,7 +60158,7 @@
         <v>46191</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60231,7 +60231,7 @@
         <v>46191</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         <v>45546</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45267</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>46196</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>46195</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45615</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>46195</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>46196</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>45107</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>45107</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>46195</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61044,7 +61044,7 @@
         <v>46195</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>45090</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>44823</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>44813</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>45310</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>46198</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44775</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>46198</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>46197</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45551</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>46197</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45443</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>46197</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>45307</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>46140</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46198</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>46197</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45282</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>46203</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>46203</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>46203</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45665</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44638</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>46206</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>46208</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>46205</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>46206</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>46209</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63196,7 +63196,7 @@
         <v>44775</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63269,7 +63269,7 @@
         <v>44775</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63342,7 +63342,7 @@
         <v>46205</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>44798</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46212</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>46211</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46212</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>46212</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>44544</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>45625</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45436</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>45587</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>46259</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45618</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46258</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>45198</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>44790</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>46261</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64545,7 +64545,7 @@
         <v>46261</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64623,7 +64623,7 @@
         <v>45302</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64696,7 +64696,7 @@
         <v>44818</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>46261</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64842,7 +64842,7 @@
         <v>45097</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>46265</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45399</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45618</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45558</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>46265</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>46153</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>46164</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>46220</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45693</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>46265</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>46108</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45772</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>46223</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>46223</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44953</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>46224</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45217</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45321</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45518</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45518</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45072</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>44700</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45593</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>44818</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46273</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>46230</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>45105</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66921,7 +66921,7 @@
         <v>46274</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>46275</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>46274</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>46275</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>46274</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>46233</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46276</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>46279</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>46279</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>46276</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67696,7 +67696,7 @@
         <v>46279</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46276</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>45168</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46237</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68003,7 +68003,7 @@
         <v>45671</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68076,7 +68076,7 @@
         <v>45672</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>45176</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>46276</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45420</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>46280</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68446,7 +68446,7 @@
         <v>46237</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68524,7 +68524,7 @@
         <v>45555</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68597,7 +68597,7 @@
         <v>44910</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68670,7 +68670,7 @@
         <v>46237</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>46280</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>46237</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68899,7 +68899,7 @@
         <v>45236</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>45722</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>45590</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69123,7 +69123,7 @@
         <v>45483</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>46239</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>45210</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>44571</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>45230</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69566,7 +69566,7 @@
         <v>45243</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69639,7 +69639,7 @@
         <v>45537</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69712,7 +69712,7 @@
         <v>46241</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69790,7 +69790,7 @@
         <v>46241</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>46198</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69946,7 +69946,7 @@
         <v>44939</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>44728</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70097,7 +70097,7 @@
         <v>45575</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70175,7 +70175,7 @@
         <v>46241</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70253,7 +70253,7 @@
         <v>44818</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70326,7 +70326,7 @@
         <v>46216</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70399,7 +70399,7 @@
         <v>46244</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70477,7 +70477,7 @@
         <v>46287</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70555,7 +70555,7 @@
         <v>45317</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70628,7 +70628,7 @@
         <v>44929</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70701,7 +70701,7 @@
         <v>46244</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>45644</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>46241</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>46246</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46289</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71081,7 +71081,7 @@
         <v>46057</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71154,7 +71154,7 @@
         <v>46248</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71232,7 +71232,7 @@
         <v>45476</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71305,7 +71305,7 @@
         <v>46171</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71383,7 +71383,7 @@
         <v>45642</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71456,7 +71456,7 @@
         <v>44637</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71529,7 +71529,7 @@
         <v>45119</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71602,7 +71602,7 @@
         <v>46248</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71680,7 +71680,7 @@
         <v>45223</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71753,7 +71753,7 @@
         <v>44806</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71826,7 +71826,7 @@
         <v>44519</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71899,7 +71899,7 @@
         <v>44875</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71972,7 +71972,7 @@
         <v>45646</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72045,7 +72045,7 @@
         <v>46239</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72118,7 +72118,7 @@
         <v>45582</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46203</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46293</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72347,7 +72347,7 @@
         <v>44841</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72420,7 +72420,7 @@
         <v>45775</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72498,7 +72498,7 @@
         <v>45098</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72571,7 +72571,7 @@
         <v>45567</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72644,7 +72644,7 @@
         <v>45182</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72717,7 +72717,7 @@
         <v>46098</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         <v>45194</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>45187</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>45072</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73019,7 +73019,7 @@
         <v>46162</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>45329</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>45204</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73238,7 +73238,7 @@
         <v>45516</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>45946</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73389,7 +73389,7 @@
         <v>46296</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>46296</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73545,7 +73545,7 @@
         <v>45194</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73618,7 +73618,7 @@
         <v>46159</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73696,7 +73696,7 @@
         <v>45349</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>45245</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73842,7 +73842,7 @@
         <v>44847</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73915,7 +73915,7 @@
         <v>45071</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73988,7 +73988,7 @@
         <v>46134</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74066,7 +74066,7 @@
         <v>45736</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74139,7 +74139,7 @@
         <v>46296</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74217,7 +74217,7 @@
         <v>46297</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74295,7 +74295,7 @@
         <v>46297</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74368,7 +74368,7 @@
         <v>45455</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74446,7 +74446,7 @@
         <v>44930</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74519,7 +74519,7 @@
         <v>44517</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>45139</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74665,7 +74665,7 @@
         <v>45231</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74738,7 +74738,7 @@
         <v>45231</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74811,7 +74811,7 @@
         <v>45534</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74884,7 +74884,7 @@
         <v>45392</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74957,7 +74957,7 @@
         <v>44997</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75030,7 +75030,7 @@
         <v>45002</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75103,7 +75103,7 @@
         <v>45259</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75176,7 +75176,7 @@
         <v>45625</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75249,7 +75249,7 @@
         <v>44746</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>45600</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
         <v>45232</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75468,7 +75468,7 @@
         <v>45756</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75541,7 +75541,7 @@
         <v>44907</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75619,7 +75619,7 @@
         <v>45582</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75692,7 +75692,7 @@
         <v>45744</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75765,7 +75765,7 @@
         <v>45190</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75838,7 +75838,7 @@
         <v>45176</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75916,7 +75916,7 @@
         <v>44866</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75989,7 +75989,7 @@
         <v>45422</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76067,7 +76067,7 @@
         <v>45516</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76140,7 +76140,7 @@
         <v>45112</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76213,7 +76213,7 @@
         <v>45334</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76286,7 +76286,7 @@
         <v>45173</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76359,7 +76359,7 @@
         <v>45586</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76437,7 +76437,7 @@
         <v>45733</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76510,7 +76510,7 @@
         <v>45525</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76583,7 +76583,7 @@
         <v>45525</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76656,7 +76656,7 @@
         <v>44551</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76729,7 +76729,7 @@
         <v>45321</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76802,7 +76802,7 @@
         <v>44804</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>45686</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45666</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77021,7 +77021,7 @@
         <v>44475</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77094,7 +77094,7 @@
         <v>45771</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77167,7 +77167,7 @@
         <v>45112</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77240,7 +77240,7 @@
         <v>45188</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77313,7 +77313,7 @@
         <v>45560</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77386,7 +77386,7 @@
         <v>45666</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77459,7 +77459,7 @@
         <v>45776</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77532,7 +77532,7 @@
         <v>45776</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>45779</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>45616</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>45782</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45279</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>45505</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>45782</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78048,7 +78048,7 @@
         <v>44799</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78126,7 +78126,7 @@
         <v>45602</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>45784</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78272,7 +78272,7 @@
         <v>45351</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78345,7 +78345,7 @@
         <v>45545</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78418,7 +78418,7 @@
         <v>45273</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78491,7 +78491,7 @@
         <v>44160</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78564,7 +78564,7 @@
         <v>44174</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78637,7 +78637,7 @@
         <v>45730</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78710,7 +78710,7 @@
         <v>45405</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78788,7 +78788,7 @@
         <v>45351</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78866,7 +78866,7 @@
         <v>45105</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78939,7 +78939,7 @@
         <v>45699</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79017,7 +79017,7 @@
         <v>45125</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79090,7 +79090,7 @@
         <v>45135</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79163,7 +79163,7 @@
         <v>44769</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79236,7 +79236,7 @@
         <v>44909</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79309,7 +79309,7 @@
         <v>45708</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79387,7 +79387,7 @@
         <v>45761</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79465,7 +79465,7 @@
         <v>45761</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79543,7 +79543,7 @@
         <v>45771</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79621,7 +79621,7 @@
         <v>45814</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79699,7 +79699,7 @@
         <v>45183</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79772,7 +79772,7 @@
         <v>46056</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79845,7 +79845,7 @@
         <v>46072</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79923,7 +79923,7 @@
         <v>46089</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80001,7 +80001,7 @@
         <v>46141</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80079,7 +80079,7 @@
         <v>46198</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44909</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>46198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45476</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44911</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45377</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45406</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45845</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>46297</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44620</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44627</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45411</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45365</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>45784</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>45926</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45194</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45426</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45359</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45961</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45841</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45694</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45996</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>46127</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>46135</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>46027</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>46042</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45243</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45985</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>46036</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>46090</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>46127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46211</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46265</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46274</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>46231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>46276</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>46276</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46276</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46112</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>46287</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>46296</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>44098</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44792</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44497</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44763</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44749</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44638</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44795</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44824</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44565</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44484</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44571</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44797</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44559</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44692</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44489</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44841</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44795</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44845</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44789</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44679</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44679</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44578</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44774</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44579</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44533</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44732</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44838</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44727</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>44484</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44799</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>44862</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45225</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45642</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45159</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44806</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44840</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45321</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45330</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44798</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44866</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45575</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45737</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45586</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45399</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45537</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45259</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45544</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45453</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45665</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45412</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>45106</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45105</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45251</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45267</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44929</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45204</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45243</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45329</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44953</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45518</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44736</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44928</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45569</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44790</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45071</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45398</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>44818</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45884</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45646</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44571</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45516</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45194</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45251</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45225</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44519</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45884</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44819</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45231</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45231</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44573</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45194</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45232</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45884</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45139</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44875</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45478</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45618</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45622</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45883</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45513</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45666</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45888</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45436</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45520</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44529</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45425</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45259</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44997</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45742</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45588</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>44939</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44889</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45321</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45775</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45700</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45895</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45895</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45236</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45902</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45253</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45541</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45337</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45483</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45537</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45615</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45539</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45539</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45432</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45639</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44890</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45905</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45905</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45671</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45392</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45539</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45124</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>44914</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44991</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45310</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45910</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45590</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45776</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45567</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45646</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45551</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45582</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45776</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45518</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45190</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>44922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45596</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45779</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45782</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45782</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44910</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45616</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45617</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45632</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45279</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45264</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45264</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45513</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45505</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45176</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45582</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45569</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45616</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45915</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45702</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45784</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45539</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45539</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45618</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45525</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45525</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45273</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45582</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45545</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45602</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45351</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45428</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45516</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45920</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45919</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45505</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45789</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45790</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44515</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45923</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45923</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45534</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45505</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45923</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45789</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45925</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45925</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45925</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45791</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45334</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45518</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45518</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45321</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45476</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45033</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45201</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45930</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45653</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45552</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>44562</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45181</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45793</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45796</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45796</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45533</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44964</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45097</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45168</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44893</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45796</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45793</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45558</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45644</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45603</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45798</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>44944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45933</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45555</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45623</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44529</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45757</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45799</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45803</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44977</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45351</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45373</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45937</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45677</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45555</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45803</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45937</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44872</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45187</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45737</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45201</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45217</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44911</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45623</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45321</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45937</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45397</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>45223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>45182</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45558</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>45686</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45112</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45939</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45939</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45940</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45939</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45940</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45377</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45943</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45943</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45562</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45560</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45943</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45930</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45672</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45666</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45628</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45755</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45813</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45363</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>44638</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45817</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44637</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45225</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45820</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45819</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45821</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45314</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45824</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45307</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45824</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45721</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44651</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45603</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45825</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45825</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45825</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45825</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45455</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45686</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45253</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45671</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45672</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45953</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45954</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45960</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45960</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45960</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45960</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45960</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45833</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45833</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45119</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45833</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45833</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>45161</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45107</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45833</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45833</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45835</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45275</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45772</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45672</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45961</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45596</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>45645</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45107</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45840</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>45679</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45840</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45422</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44826</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45965</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>44728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44907</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45966</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45664</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45965</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45967</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>45968</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45967</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45967</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45625</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45695</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45971</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45971</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45971</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44719</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>45636</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45202</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45733</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45972</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45971</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44813</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45847</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45615</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45973</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>44897</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45974</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45974</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45974</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45849</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>45659</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45973</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45849</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45148</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45756</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45853</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45210</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>44798</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45776</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45726</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>45317</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45173</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44680</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>44519</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>45534</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>44775</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45975</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45173</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45231</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45231</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45874</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45021</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45874</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45637</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45362</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>45393</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45223</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>44823</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45686</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45803</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45771</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45321</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45877</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45877</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45981</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>45072</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45072</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45358</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45215</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45881</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45881</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45267</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45882</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>45588</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45744</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45097</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>46098</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>46098</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>46099</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>46099</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>44847</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46094</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45986</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46100</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45985</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45985</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45077</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45985</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45344</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45176</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>46105</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46104</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46105</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45985</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45985</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>46105</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44911</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45986</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45671</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>46106</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44641</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>46106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>46106</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45987</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45988</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45093</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45537</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45071</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45989</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45989</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45992</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46112</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>44818</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45517</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45259</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45587</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45994</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>44841</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45547</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45523</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45539</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45994</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46125</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>44746</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46122</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>46122</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>44621</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>46127</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44964</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>46126</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46126</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46000</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46000</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>45999</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46000</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45999</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46127</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45555</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>44762</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>44602</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>44796</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>44742</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46129</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46133</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>44807</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45443</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45925</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>46003</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45925</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45302</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45539</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>44930</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45733</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45264</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>46010</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46010</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46010</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>46010</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45737</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45784</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>46136</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>46104</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>46009</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>46010</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45379</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>46037</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45958</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45621</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46050</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46098</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45258</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>46063</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45481</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45679</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45266</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45229</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45230</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>46027</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>46027</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>46027</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46057</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>46027</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45939</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45888</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45916</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>46030</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>45257</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45245</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>45245</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>45107</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57158,7 +57158,7 @@
         <v>44960</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>44882</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>46085</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57382,7 +57382,7 @@
         <v>46031</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45840</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>46136</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>46139</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46033</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45440</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46033</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>46033</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57976,7 +57976,7 @@
         <v>45567</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46034</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>46042</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>45324</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58268,7 +58268,7 @@
         <v>46036</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58341,7 +58341,7 @@
         <v>45595</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45989</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58487,7 +58487,7 @@
         <v>44700</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45961</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>44684</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>46027</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>45098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45002</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>46027</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>46036</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
         <v>45943</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59149,7 +59149,7 @@
         <v>46036</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>46036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>46029</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>46042</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>46042</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>44746</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>46042</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59660,7 +59660,7 @@
         <v>45560</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>45019</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59806,7 +59806,7 @@
         <v>45019</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59879,7 +59879,7 @@
         <v>46139</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>46035</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46038</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>46033</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45825</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>46042</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>45194</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>46050</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>46044</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>46139</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>46044</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>46048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60906,7 +60906,7 @@
         <v>46044</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45776</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>46139</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61125,7 +61125,7 @@
         <v>45810</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45666</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61271,7 +61271,7 @@
         <v>46048</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>44644</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>45841</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61495,7 +61495,7 @@
         <v>44930</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>44930</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>44834</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>46048</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61787,7 +61787,7 @@
         <v>46029</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45266</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45344</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62006,7 +62006,7 @@
         <v>46048</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45245</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>45797</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>46083</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>46025</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>46025</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45590</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45586</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>46049</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46049</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45618</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>46019</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>46141</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>46141</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63038,7 +63038,7 @@
         <v>46083</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45611</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63184,7 +63184,7 @@
         <v>46050</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45799</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63330,7 +63330,7 @@
         <v>46062</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>46105</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63481,7 +63481,7 @@
         <v>45930</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>46141</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>46141</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>46141</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>46142</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63866,7 +63866,7 @@
         <v>46050</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63939,7 +63939,7 @@
         <v>46056</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>46057</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         <v>46132</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64163,7 +64163,7 @@
         <v>45896</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64236,7 +64236,7 @@
         <v>46052</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>46106</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>45957</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64465,7 +64465,7 @@
         <v>46062</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>46062</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>46036</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>46070</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>46062</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>46062</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45686</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>46084</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>46064</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>46146</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>46064</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45972</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>45968</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>46063</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>46079</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>46146</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>46066</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>46066</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>46065</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65935,7 +65935,7 @@
         <v>46066</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>46148</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>46148</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66164,7 +66164,7 @@
         <v>46148</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66242,7 +66242,7 @@
         <v>46148</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>46070</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>46069</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>46149</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>45267</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>46072</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66695,7 +66695,7 @@
         <v>45575</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>46085</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>46064</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>46106</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>46048</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>46073</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>46073</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46072</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46113</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>46078</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45952</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67533,7 +67533,7 @@
         <v>46055</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67606,7 +67606,7 @@
         <v>46079</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67684,7 +67684,7 @@
         <v>46155</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>46104</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67835,7 +67835,7 @@
         <v>46105</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>46085</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>46085</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>46086</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68132,7 +68132,7 @@
         <v>46068</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>46090</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68278,7 +68278,7 @@
         <v>46090</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68351,7 +68351,7 @@
         <v>46157</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68424,7 +68424,7 @@
         <v>46162</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>46070</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68570,7 +68570,7 @@
         <v>45646</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68643,7 +68643,7 @@
         <v>46139</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>46105</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>46052</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>46167</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68940,7 +68940,7 @@
         <v>46056</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>46105</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>46175</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69164,7 +69164,7 @@
         <v>46175</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69237,7 +69237,7 @@
         <v>46078</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69310,7 +69310,7 @@
         <v>46178</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69388,7 +69388,7 @@
         <v>46178</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>46141</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>46178</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>46140</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69690,7 +69690,7 @@
         <v>46121</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69763,7 +69763,7 @@
         <v>45968</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>46184</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>46184</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>46189</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70065,7 +70065,7 @@
         <v>45672</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>46191</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>46190</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>46191</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>46191</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>46190</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>46191</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70581,7 +70581,7 @@
         <v>46195</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70654,7 +70654,7 @@
         <v>46195</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70732,7 +70732,7 @@
         <v>46195</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70810,7 +70810,7 @@
         <v>46195</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>46043</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>46197</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>46197</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>46140</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>46197</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71258,7 +71258,7 @@
         <v>46197</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71331,7 +71331,7 @@
         <v>46196</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71404,7 +71404,7 @@
         <v>46196</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71477,7 +71477,7 @@
         <v>46198</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71555,7 +71555,7 @@
         <v>46198</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71633,7 +71633,7 @@
         <v>46198</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71711,7 +71711,7 @@
         <v>46203</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71784,7 +71784,7 @@
         <v>46203</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71857,7 +71857,7 @@
         <v>46203</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71930,7 +71930,7 @@
         <v>46205</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>46209</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72076,7 +72076,7 @@
         <v>46206</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72149,7 +72149,7 @@
         <v>46206</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72227,7 +72227,7 @@
         <v>46208</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72300,7 +72300,7 @@
         <v>46206</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72373,7 +72373,7 @@
         <v>46205</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72446,7 +72446,7 @@
         <v>46211</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72519,7 +72519,7 @@
         <v>46212</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72597,7 +72597,7 @@
         <v>46212</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72675,7 +72675,7 @@
         <v>45693</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72753,7 +72753,7 @@
         <v>46224</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72826,7 +72826,7 @@
         <v>46265</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72904,7 +72904,7 @@
         <v>46220</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72977,7 +72977,7 @@
         <v>46265</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73050,7 +73050,7 @@
         <v>46153</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73128,7 +73128,7 @@
         <v>46164</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73206,7 +73206,7 @@
         <v>46265</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73279,7 +73279,7 @@
         <v>46108</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73357,7 +73357,7 @@
         <v>46223</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73430,7 +73430,7 @@
         <v>46223</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73503,7 +73503,7 @@
         <v>46274</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73581,7 +73581,7 @@
         <v>46274</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73659,7 +73659,7 @@
         <v>46273</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73737,7 +73737,7 @@
         <v>46274</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73815,7 +73815,7 @@
         <v>46230</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73888,7 +73888,7 @@
         <v>46276</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73966,7 +73966,7 @@
         <v>46276</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74044,7 +74044,7 @@
         <v>46276</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74122,7 +74122,7 @@
         <v>46233</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74200,7 +74200,7 @@
         <v>46275</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74278,7 +74278,7 @@
         <v>46279</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74356,7 +74356,7 @@
         <v>46279</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>46237</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74507,7 +74507,7 @@
         <v>46279</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74580,7 +74580,7 @@
         <v>46237</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>46280</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74736,7 +74736,7 @@
         <v>46280</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74809,7 +74809,7 @@
         <v>46237</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74887,7 +74887,7 @@
         <v>46276</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74960,7 +74960,7 @@
         <v>46237</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75038,7 +75038,7 @@
         <v>46239</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75111,7 +75111,7 @@
         <v>46283</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75184,7 +75184,7 @@
         <v>46241</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75262,7 +75262,7 @@
         <v>46198</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75340,7 +75340,7 @@
         <v>46216</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75413,7 +75413,7 @@
         <v>46241</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75491,7 +75491,7 @@
         <v>46241</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75569,7 +75569,7 @@
         <v>46241</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75647,7 +75647,7 @@
         <v>46287</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75725,7 +75725,7 @@
         <v>46244</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75803,7 +75803,7 @@
         <v>46244</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75881,7 +75881,7 @@
         <v>46171</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75959,7 +75959,7 @@
         <v>46289</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>46162</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>46248</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46293</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76266,7 +76266,7 @@
         <v>46248</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76344,7 +76344,7 @@
         <v>46239</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>46203</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76495,7 +76495,7 @@
         <v>46098</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76568,7 +76568,7 @@
         <v>46296</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76646,7 +76646,7 @@
         <v>46296</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         <v>46300</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76797,7 +76797,7 @@
         <v>46134</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>46300</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45910</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         <v>46297</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77104,7 +77104,7 @@
         <v>46300</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77177,7 +77177,7 @@
         <v>46159</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>46057</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>46300</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>46300</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45946</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>46297</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77620,7 +77620,7 @@
         <v>46259</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77693,7 +77693,7 @@
         <v>46301</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77766,7 +77766,7 @@
         <v>46258</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77844,7 +77844,7 @@
         <v>45736</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77917,7 +77917,7 @@
         <v>45862</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>46303</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>46303</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78136,7 +78136,7 @@
         <v>46303</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78209,7 +78209,7 @@
         <v>46303</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78282,7 +78282,7 @@
         <v>46261</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78360,7 +78360,7 @@
         <v>46261</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78438,7 +78438,7 @@
         <v>46303</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>46304</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78584,7 +78584,7 @@
         <v>46261</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78657,7 +78657,7 @@
         <v>46212</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78735,7 +78735,7 @@
         <v>46303</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78808,7 +78808,7 @@
         <v>46275</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78886,7 +78886,7 @@
         <v>45835</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45730</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>44160</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79110,7 +79110,7 @@
         <v>44174</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79183,7 +79183,7 @@
         <v>45405</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>45351</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79339,7 +79339,7 @@
         <v>45105</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79412,7 +79412,7 @@
         <v>45699</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79490,7 +79490,7 @@
         <v>45125</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79563,7 +79563,7 @@
         <v>45135</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79636,7 +79636,7 @@
         <v>44769</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79709,7 +79709,7 @@
         <v>44909</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79782,7 +79782,7 @@
         <v>45708</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79860,7 +79860,7 @@
         <v>45761</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79938,7 +79938,7 @@
         <v>45761</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80016,7 +80016,7 @@
         <v>45771</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80094,7 +80094,7 @@
         <v>45814</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>45183</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>46056</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>46072</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>46089</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80474,7 +80474,7 @@
         <v>46141</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80552,7 +80552,7 @@
         <v>46198</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44909</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>46198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45476</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44911</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45377</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45406</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45845</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>46297</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44620</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44627</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45411</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45365</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>45784</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>45926</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45194</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45426</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45359</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45961</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45841</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45694</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45996</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>46127</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>46135</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>46027</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>46042</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45243</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45985</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>46036</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>46090</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>46127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46211</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46265</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46274</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>46231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>46276</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>46276</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46276</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46112</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>46287</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>46296</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>44098</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44792</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44495</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44497</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44763</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44749</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44638</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44795</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44824</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44565</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44484</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44571</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44797</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44559</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44692</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44489</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44841</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44795</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44845</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44789</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44679</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44679</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44578</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44774</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44579</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44533</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44732</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44838</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44727</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>44484</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44799</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>44862</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45225</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45642</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45159</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44806</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44840</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45321</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45330</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44798</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44866</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45575</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45737</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45586</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45399</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45537</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45259</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45544</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45453</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45665</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45412</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>45106</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45105</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45251</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45267</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44929</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45204</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45243</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45329</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44953</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45518</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44736</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44928</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45569</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44790</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45071</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45398</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>44818</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45884</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45646</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44571</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45516</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45194</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45251</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45225</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44519</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45884</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44819</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45231</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45231</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44573</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45194</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45232</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45884</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45139</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44875</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45478</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45618</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45622</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45883</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45513</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45666</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45888</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45436</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45520</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44529</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45425</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45259</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44997</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45742</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45588</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>44939</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44889</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45321</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45775</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45700</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45895</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45895</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45236</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45902</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45253</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45541</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45337</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45483</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45537</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45615</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45539</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45539</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45432</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45639</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44890</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45905</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45905</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45671</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45392</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45539</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45124</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>44914</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44991</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45310</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45910</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45590</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45776</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45567</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45646</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45551</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45582</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45776</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45518</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45190</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>44922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45596</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45779</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45782</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45782</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44910</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45616</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45617</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45632</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45279</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45264</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45264</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45513</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45505</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45176</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45582</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45569</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45616</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45915</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45702</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45784</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45539</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45539</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45618</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45525</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45525</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45273</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45582</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45545</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45602</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45351</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45428</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45516</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45920</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45919</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45505</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45789</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45790</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44515</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45923</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45923</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45534</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45505</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45923</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45923</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45789</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45925</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45925</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45925</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45791</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45334</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45518</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45518</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45321</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45476</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45033</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45201</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45930</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45653</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45552</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>44562</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45181</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45793</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45796</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45796</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45533</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44964</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45097</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45168</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44893</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45796</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45793</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45558</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45644</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45603</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45798</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>44944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45933</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45555</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45623</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44529</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45757</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45799</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45803</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44977</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45351</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45373</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45937</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45677</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45555</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45803</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45937</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44872</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45187</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45737</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45201</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45217</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44911</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45623</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45321</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45937</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45397</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>45223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>45182</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45558</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>45686</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45112</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45939</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45939</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45940</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45939</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45940</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45377</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45943</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45943</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45562</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45560</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45943</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45930</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45672</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45666</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45628</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45755</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45813</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45363</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>44638</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45817</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44637</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45225</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45820</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45819</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45821</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45314</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45824</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45307</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45824</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45721</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>44651</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45603</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45825</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45825</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45825</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45825</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45455</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45686</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45253</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45671</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45672</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45953</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45954</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45960</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45960</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45960</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45960</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45960</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45833</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>45833</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45119</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45833</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45833</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>45161</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45107</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45833</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45833</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45835</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45275</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45772</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45672</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45961</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45596</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>45645</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45107</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45840</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>45679</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45840</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45422</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44826</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45965</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>44728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44907</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45966</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45664</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45965</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45967</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>45968</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45967</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45967</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45625</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45695</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45971</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45971</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45971</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>44719</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>45636</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45202</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45733</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45972</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45971</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44813</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45847</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45615</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45973</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>44897</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45974</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45974</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45974</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45849</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>45659</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45973</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45849</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45148</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45756</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45853</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45210</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>44798</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45776</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45726</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>45317</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45173</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44680</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>44519</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>45534</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>44775</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45975</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45173</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45231</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45231</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45874</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45021</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45874</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45637</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45362</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>45393</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45223</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>44823</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45686</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45803</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45771</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45321</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45877</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45877</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45981</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>45072</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45072</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45358</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45215</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45881</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45881</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45267</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45882</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>45588</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45744</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45097</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>46098</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>46098</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>46099</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48477,7 +48477,7 @@
         <v>46099</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>44847</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46094</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45986</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46100</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45985</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45985</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45077</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45985</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45344</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45176</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>46105</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46104</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46105</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45985</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45985</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>46105</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44911</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45986</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45671</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>46106</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44641</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>46106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>46106</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45987</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45988</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45093</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45537</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45071</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45989</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45989</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45992</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46112</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>44818</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45517</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45259</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45587</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45994</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>44841</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45547</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45523</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45539</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45994</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46125</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>44746</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46122</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>46122</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>44621</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>46127</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44964</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>46126</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>46126</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46000</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46000</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>45999</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46000</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45999</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46127</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45555</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>44762</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>44602</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>44796</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>44742</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46129</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46133</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>44807</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45443</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45925</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>46003</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45925</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45302</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45539</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>44930</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45733</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45264</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>46010</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>46010</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46010</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>46010</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45737</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>45784</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>46136</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>46104</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55109,7 +55109,7 @@
         <v>46009</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55182,7 +55182,7 @@
         <v>46010</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45379</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>46037</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45958</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>45621</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46050</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>46098</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45258</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>46063</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45481</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45679</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45266</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45229</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56131,7 +56131,7 @@
         <v>45230</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>46027</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>46027</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>46027</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46057</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>46027</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45939</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45888</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45916</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>46030</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>45257</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45245</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>45245</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>45107</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57158,7 +57158,7 @@
         <v>44960</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>44882</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>46085</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57382,7 +57382,7 @@
         <v>46031</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45840</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>46136</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>46139</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46033</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45440</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46033</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>46033</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57976,7 +57976,7 @@
         <v>45567</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46034</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>46042</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>45324</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58268,7 +58268,7 @@
         <v>46036</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58341,7 +58341,7 @@
         <v>45595</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45989</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58487,7 +58487,7 @@
         <v>44700</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45961</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>44684</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>46027</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>45098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45002</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>46027</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>46036</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
         <v>45943</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59149,7 +59149,7 @@
         <v>46036</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>46036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59295,7 +59295,7 @@
         <v>46029</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>46042</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>46042</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>44746</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>46042</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59660,7 +59660,7 @@
         <v>45560</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>45019</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59806,7 +59806,7 @@
         <v>45019</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59879,7 +59879,7 @@
         <v>46139</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>46035</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46038</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>46033</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45825</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>46042</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>45194</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>46050</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>46044</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>46139</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>46044</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>46048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60906,7 +60906,7 @@
         <v>46044</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45776</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>46139</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61125,7 +61125,7 @@
         <v>45810</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45666</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61271,7 +61271,7 @@
         <v>46048</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>44644</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>45841</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61495,7 +61495,7 @@
         <v>44930</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>44930</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>44834</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>46048</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61787,7 +61787,7 @@
         <v>46029</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45266</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45344</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62006,7 +62006,7 @@
         <v>46048</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45245</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>45797</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>46083</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>46025</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>46025</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45590</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45586</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>46049</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46049</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45618</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>46019</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>46141</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>46141</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63038,7 +63038,7 @@
         <v>46083</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45611</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63184,7 +63184,7 @@
         <v>46050</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45799</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63330,7 +63330,7 @@
         <v>46062</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>46105</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63481,7 +63481,7 @@
         <v>45930</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>46141</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>46141</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>46141</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>46142</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63866,7 +63866,7 @@
         <v>46050</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63939,7 +63939,7 @@
         <v>46056</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>46057</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         <v>46132</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64163,7 +64163,7 @@
         <v>45896</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64236,7 +64236,7 @@
         <v>46052</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>46106</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>45957</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64465,7 +64465,7 @@
         <v>46062</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>46062</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>46036</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>46070</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>46062</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>46062</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45686</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>46084</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>46064</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>46146</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>46064</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45972</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>45968</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>46063</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>46079</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>46146</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>46066</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>46066</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>46065</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65935,7 +65935,7 @@
         <v>46066</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>46148</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>46148</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66164,7 +66164,7 @@
         <v>46148</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66242,7 +66242,7 @@
         <v>46148</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>46070</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>46069</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>46149</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>45267</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>46072</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66695,7 +66695,7 @@
         <v>45575</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>46085</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>46064</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>46106</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>46048</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>46073</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>46073</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46072</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46113</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>46078</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45952</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67533,7 +67533,7 @@
         <v>46055</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67606,7 +67606,7 @@
         <v>46079</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67684,7 +67684,7 @@
         <v>46155</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>46104</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67835,7 +67835,7 @@
         <v>46105</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>46085</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>46085</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>46086</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68132,7 +68132,7 @@
         <v>46068</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>46090</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68278,7 +68278,7 @@
         <v>46090</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68351,7 +68351,7 @@
         <v>46157</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68424,7 +68424,7 @@
         <v>46162</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>46070</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68570,7 +68570,7 @@
         <v>45646</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68643,7 +68643,7 @@
         <v>46139</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>46105</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>46052</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>46167</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68940,7 +68940,7 @@
         <v>46056</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>46105</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>46175</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69164,7 +69164,7 @@
         <v>46175</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69237,7 +69237,7 @@
         <v>46078</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69310,7 +69310,7 @@
         <v>46178</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69388,7 +69388,7 @@
         <v>46178</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>46141</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>46178</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>46140</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69690,7 +69690,7 @@
         <v>46121</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69763,7 +69763,7 @@
         <v>45968</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>46184</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>46184</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>46189</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70065,7 +70065,7 @@
         <v>45672</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>46191</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>46190</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>46191</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>46191</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>46190</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>46191</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70581,7 +70581,7 @@
         <v>46195</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70654,7 +70654,7 @@
         <v>46195</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70732,7 +70732,7 @@
         <v>46195</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70810,7 +70810,7 @@
         <v>46195</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>46043</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>46197</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>46197</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>46140</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>46197</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71258,7 +71258,7 @@
         <v>46197</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71331,7 +71331,7 @@
         <v>46196</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71404,7 +71404,7 @@
         <v>46196</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71477,7 +71477,7 @@
         <v>46198</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71555,7 +71555,7 @@
         <v>46198</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71633,7 +71633,7 @@
         <v>46198</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71711,7 +71711,7 @@
         <v>46203</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71784,7 +71784,7 @@
         <v>46203</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71857,7 +71857,7 @@
         <v>46203</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71930,7 +71930,7 @@
         <v>46205</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>46209</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72076,7 +72076,7 @@
         <v>46206</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72149,7 +72149,7 @@
         <v>46206</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72227,7 +72227,7 @@
         <v>46208</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72300,7 +72300,7 @@
         <v>46206</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72373,7 +72373,7 @@
         <v>46205</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72446,7 +72446,7 @@
         <v>46211</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72519,7 +72519,7 @@
         <v>46212</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72597,7 +72597,7 @@
         <v>46212</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72675,7 +72675,7 @@
         <v>45693</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72753,7 +72753,7 @@
         <v>46224</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72826,7 +72826,7 @@
         <v>46265</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72904,7 +72904,7 @@
         <v>46220</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72977,7 +72977,7 @@
         <v>46265</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73050,7 +73050,7 @@
         <v>46153</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73128,7 +73128,7 @@
         <v>46164</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73206,7 +73206,7 @@
         <v>46265</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73279,7 +73279,7 @@
         <v>46108</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73357,7 +73357,7 @@
         <v>46223</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73430,7 +73430,7 @@
         <v>46223</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73503,7 +73503,7 @@
         <v>46274</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73581,7 +73581,7 @@
         <v>46274</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73659,7 +73659,7 @@
         <v>46273</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73737,7 +73737,7 @@
         <v>46274</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73815,7 +73815,7 @@
         <v>46230</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73888,7 +73888,7 @@
         <v>46276</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73966,7 +73966,7 @@
         <v>46276</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74044,7 +74044,7 @@
         <v>46276</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74122,7 +74122,7 @@
         <v>46233</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74200,7 +74200,7 @@
         <v>46275</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74278,7 +74278,7 @@
         <v>46279</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74356,7 +74356,7 @@
         <v>46279</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>46237</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74507,7 +74507,7 @@
         <v>46279</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74580,7 +74580,7 @@
         <v>46237</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>46280</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74736,7 +74736,7 @@
         <v>46280</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74809,7 +74809,7 @@
         <v>46237</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74887,7 +74887,7 @@
         <v>46276</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74960,7 +74960,7 @@
         <v>46237</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75038,7 +75038,7 @@
         <v>46239</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75111,7 +75111,7 @@
         <v>46283</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75184,7 +75184,7 @@
         <v>46241</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75262,7 +75262,7 @@
         <v>46198</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75340,7 +75340,7 @@
         <v>46216</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75413,7 +75413,7 @@
         <v>46241</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75491,7 +75491,7 @@
         <v>46241</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75569,7 +75569,7 @@
         <v>46241</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75647,7 +75647,7 @@
         <v>46287</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75725,7 +75725,7 @@
         <v>46244</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75803,7 +75803,7 @@
         <v>46244</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75881,7 +75881,7 @@
         <v>46171</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75959,7 +75959,7 @@
         <v>46289</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>46162</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>46248</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46293</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76266,7 +76266,7 @@
         <v>46248</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76344,7 +76344,7 @@
         <v>46239</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>46203</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76495,7 +76495,7 @@
         <v>46098</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76568,7 +76568,7 @@
         <v>46296</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76646,7 +76646,7 @@
         <v>46296</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         <v>46300</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76797,7 +76797,7 @@
         <v>46134</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>46300</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45910</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         <v>46297</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77104,7 +77104,7 @@
         <v>46300</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77177,7 +77177,7 @@
         <v>46159</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>46057</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>46300</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>46300</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45946</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>46297</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77620,7 +77620,7 @@
         <v>46259</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77693,7 +77693,7 @@
         <v>46301</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77766,7 +77766,7 @@
         <v>46258</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77844,7 +77844,7 @@
         <v>45736</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77917,7 +77917,7 @@
         <v>45862</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>46303</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>46303</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78136,7 +78136,7 @@
         <v>46303</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78209,7 +78209,7 @@
         <v>46303</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78282,7 +78282,7 @@
         <v>46261</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78360,7 +78360,7 @@
         <v>46261</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78438,7 +78438,7 @@
         <v>46303</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>46304</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78584,7 +78584,7 @@
         <v>46261</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78657,7 +78657,7 @@
         <v>46212</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78735,7 +78735,7 @@
         <v>46303</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78808,7 +78808,7 @@
         <v>46275</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78886,7 +78886,7 @@
         <v>45835</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45730</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>44160</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79110,7 +79110,7 @@
         <v>44174</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79183,7 +79183,7 @@
         <v>45405</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>45351</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79339,7 +79339,7 @@
         <v>45105</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79412,7 +79412,7 @@
         <v>45699</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79490,7 +79490,7 @@
         <v>45125</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79563,7 +79563,7 @@
         <v>45135</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79636,7 +79636,7 @@
         <v>44769</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79709,7 +79709,7 @@
         <v>44909</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79782,7 +79782,7 @@
         <v>45708</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79860,7 +79860,7 @@
         <v>45761</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79938,7 +79938,7 @@
         <v>45761</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80016,7 +80016,7 @@
         <v>45771</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80094,7 +80094,7 @@
         <v>45814</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>45183</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>46056</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>46072</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>46089</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80474,7 +80474,7 @@
         <v>46141</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80552,7 +80552,7 @@
         <v>46198</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46007</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45476</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46052</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45534</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44911</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45222</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>46274</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45406</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>46297</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>46311</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45825</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45831</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>45845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45231</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45321</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45525</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45194</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45359</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46027</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45894</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>46036</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45911</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45926</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45961</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44511</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45971</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46127</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46042</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45546</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>46127</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45985</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>46135</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45426</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>46231</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>46276</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>46276</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>46287</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>46112</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45365</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46296</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45784</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45490</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>46265</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46311</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45841</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44098</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44495</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44536</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44497</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44610</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44488</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44638</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44790</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44795</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44795</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44791</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44824</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44833</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44733</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44692</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>44727</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44862</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44638</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44762</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44845</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44533</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44839</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44839</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>44841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44679</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44579</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44732</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44795</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44578</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44748</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45321</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45432</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44930</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44651</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45425</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44826</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45555</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44719</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45596</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44893</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45517</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45351</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45093</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44602</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45299</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45321</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45344</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45231</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45201</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45478</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45321</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45344</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45518</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45225</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45677</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45363</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45321</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45225</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44991</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45173</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44872</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45398</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44922</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45194</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45352</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45513</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45755</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45453</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45300</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45362</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45201</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45562</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45653</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45539</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45033</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45337</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45757</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45275</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45412</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>44736</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45019</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45019</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45310</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44621</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>44944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45666</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45679</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45513</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45155</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45645</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45671</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45229</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46029</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>46033</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>46098</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45943</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45840</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45481</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45961</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45621</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45679</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45586</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45884</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45615</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45884</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46139</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45776</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45797</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45618</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>46049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45841</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45659</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44529</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45264</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45888</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45916</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46139</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45181</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45895</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45894</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45989</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45259</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45896</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46139</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45784</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45637</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45898</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45379</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45884</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45124</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45611</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46036</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46048</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45957</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45440</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45314</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46062</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45077</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46025</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>46042</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>46057</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45567</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46084</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46083</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>46141</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>46141</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46048</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>46019</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45896</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45588</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>46037</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46105</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46063</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46044</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45902</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45569</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45297</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45905</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45539</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45321</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45905</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>46106</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45107</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44644</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45939</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45590</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45908</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45245</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>46141</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45225</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45209</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46062</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45534</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45930</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46141</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45686</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45910</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46027</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46142</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45972</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45915</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>46052</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45915</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45916</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>44796</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>46146</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45919</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45358</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45920</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44928</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45923</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45923</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45923</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45923</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>46079</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45925</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>46148</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46149</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>46148</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45925</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45925</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>44515</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46148</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>46148</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44641</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45952</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45930</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46085</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45930</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45933</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45603</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45575</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45266</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45937</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45937</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44684</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>46064</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45539</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45937</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>46106</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45939</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45259</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45939</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44977</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45569</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45537</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45686</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45943</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45943</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44897</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45943</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45940</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>45940</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45943</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44762</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>46113</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45334</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45623</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>46105</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45539</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45930</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45646</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>46155</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45950</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45267</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45953</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45953</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>46048</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>44529</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45330</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45954</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>46055</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45174</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45957</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45251</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45672</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45958</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45958</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46157</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45245</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45960</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45960</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45960</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45961</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45960</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45960</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45541</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45721</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45167</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45965</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45520</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45965</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44964</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45537</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45967</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45967</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45967</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45971</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45537</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45616</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45971</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45971</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45968</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45973</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45972</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>46162</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45973</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45974</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45974</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45974</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45975</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>44746</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44914</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44960</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46167</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45737</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45985</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45397</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45985</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44911</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45985</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45985</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45985</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45264</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45985</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45985</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45986</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45618</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45986</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45987</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>45986</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45321</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45988</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45646</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45989</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45989</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44562</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45176</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45992</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45695</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45161</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>46105</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44807</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45994</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>46052</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45999</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45999</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46000</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46056</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46139</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>46105</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45264</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46000</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>46003</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45603</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45324</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45925</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45588</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>46009</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>46010</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46010</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46010</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46010</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45632</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44939</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45958</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45622</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46027</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46027</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46027</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46027</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46175</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>46175</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45617</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45639</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>44519</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46031</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45536</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>46030</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>46033</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46034</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46033</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>46027</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46033</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>46178</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>46036</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>46036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>46036</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>46141</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>46078</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45159</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>46042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46038</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>46178</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46042</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46042</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>46042</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>46178</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>46044</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>46044</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45737</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>46048</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>46048</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45546</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48673,7 +48673,7 @@
         <v>45267</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>46050</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46140</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45615</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45107</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>45107</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44823</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>46121</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>44813</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46056</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45310</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46057</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44775</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45551</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45443</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45307</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46063</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46184</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46062</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>46062</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>46064</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46065</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46066</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46066</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46066</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45968</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46069</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46070</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46072</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46072</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46073</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>46073</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>46078</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45665</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46079</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>44638</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46085</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>46085</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46068</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>46086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>46090</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>46090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46190</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>44775</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>44775</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>44798</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>46190</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46070</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46189</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46191</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45672</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46043</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46191</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>46191</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>44544</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>46098</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>45625</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46094</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45436</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45587</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>46196</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45618</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>46100</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>46195</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>46099</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>46098</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46099</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46195</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46196</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>46195</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>46104</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>44790</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46105</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>45302</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>46106</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>44818</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>46106</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45097</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>46106</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55275,7 +55275,7 @@
         <v>46105</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45399</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45618</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46107</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55572,7 +55572,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45558</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>46050</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>46197</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46197</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46197</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>46140</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>46112</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>46198</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45772</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>46197</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>44953</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>46122</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>46122</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>45217</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46126</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>45321</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46126</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46125</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45518</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45518</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57213,7 +57213,7 @@
         <v>45072</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>44700</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46127</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45593</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46129</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>46127</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>44818</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46203</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46133</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>46203</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>45105</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>46136</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45168</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45595</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>46029</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45671</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>45672</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>45176</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46203</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46136</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45555</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>44910</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45257</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45888</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>46025</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46139</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46206</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>45236</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>46208</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45810</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45722</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45590</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>46205</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>46206</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>46206</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45483</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46209</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>44571</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>46211</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>46212</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>45230</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45243</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>46212</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60558,7 +60558,7 @@
         <v>45537</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>44939</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>44728</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60782,7 +60782,7 @@
         <v>45575</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60860,7 +60860,7 @@
         <v>44818</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45317</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61006,7 +61006,7 @@
         <v>44929</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>45644</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>46153</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>46164</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>46220</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45693</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>46108</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>46223</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         <v>46223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61683,7 +61683,7 @@
         <v>46224</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45476</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61829,7 +61829,7 @@
         <v>46273</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61907,7 +61907,7 @@
         <v>46230</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45642</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>44637</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62126,7 +62126,7 @@
         <v>45119</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62199,7 +62199,7 @@
         <v>45223</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>44806</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>46274</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>44519</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62496,7 +62496,7 @@
         <v>44875</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>45646</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62642,7 +62642,7 @@
         <v>46274</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>45582</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62793,7 +62793,7 @@
         <v>46275</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>46274</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>44841</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63022,7 +63022,7 @@
         <v>45775</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>45098</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>46233</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>46276</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45567</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>46279</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45182</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>46279</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45194</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63704,7 +63704,7 @@
         <v>46276</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63782,7 +63782,7 @@
         <v>46279</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>46276</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>45187</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>46237</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>45072</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64167,7 +64167,7 @@
         <v>45329</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64240,7 +64240,7 @@
         <v>46276</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>46280</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>46237</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
         <v>45204</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64537,7 +64537,7 @@
         <v>45516</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>46237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>46280</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64766,7 +64766,7 @@
         <v>46237</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>46239</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>46283</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64990,7 +64990,7 @@
         <v>45194</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65063,7 +65063,7 @@
         <v>45349</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45245</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65209,7 +65209,7 @@
         <v>44847</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65282,7 +65282,7 @@
         <v>45071</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65355,7 +65355,7 @@
         <v>45455</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>44930</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>44517</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45139</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65652,7 +65652,7 @@
         <v>46241</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65730,7 +65730,7 @@
         <v>46241</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65808,7 +65808,7 @@
         <v>45231</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>45231</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65954,7 +65954,7 @@
         <v>45534</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>45392</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66100,7 +66100,7 @@
         <v>44997</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>46198</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66251,7 +66251,7 @@
         <v>45002</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66324,7 +66324,7 @@
         <v>45259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>45625</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66470,7 +66470,7 @@
         <v>46241</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>46216</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>46287</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>46244</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66855,7 +66855,7 @@
         <v>44746</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66928,7 +66928,7 @@
         <v>46241</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67006,7 +67006,7 @@
         <v>45600</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67079,7 +67079,7 @@
         <v>45232</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>46289</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67230,7 +67230,7 @@
         <v>45756</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67303,7 +67303,7 @@
         <v>44907</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45582</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>46248</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67532,7 +67532,7 @@
         <v>45744</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67605,7 +67605,7 @@
         <v>45190</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67678,7 +67678,7 @@
         <v>46171</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67756,7 +67756,7 @@
         <v>45176</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>44866</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>46248</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>45422</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68063,7 +68063,7 @@
         <v>45516</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68136,7 +68136,7 @@
         <v>45112</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68209,7 +68209,7 @@
         <v>46239</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>45334</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68355,7 +68355,7 @@
         <v>45173</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68428,7 +68428,7 @@
         <v>46203</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68506,7 +68506,7 @@
         <v>46293</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68584,7 +68584,7 @@
         <v>45586</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68662,7 +68662,7 @@
         <v>46098</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68735,7 +68735,7 @@
         <v>45733</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68808,7 +68808,7 @@
         <v>45525</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45525</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68954,7 +68954,7 @@
         <v>44551</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69027,7 +69027,7 @@
         <v>45321</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69100,7 +69100,7 @@
         <v>44804</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69173,7 +69173,7 @@
         <v>45686</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69246,7 +69246,7 @@
         <v>45666</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69319,7 +69319,7 @@
         <v>45946</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69392,7 +69392,7 @@
         <v>45771</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69465,7 +69465,7 @@
         <v>46296</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>46159</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69621,7 +69621,7 @@
         <v>45112</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>46134</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69772,7 +69772,7 @@
         <v>46296</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>46297</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69928,7 +69928,7 @@
         <v>46297</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70001,7 +70001,7 @@
         <v>45188</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>45560</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45666</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70220,7 +70220,7 @@
         <v>46300</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70293,7 +70293,7 @@
         <v>45776</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70366,7 +70366,7 @@
         <v>45776</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>46057</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>45779</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70590,7 +70590,7 @@
         <v>46300</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70663,7 +70663,7 @@
         <v>45616</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70736,7 +70736,7 @@
         <v>45782</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70809,7 +70809,7 @@
         <v>45279</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>45505</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>46300</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>45782</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>46258</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71179,7 +71179,7 @@
         <v>44799</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71257,7 +71257,7 @@
         <v>45910</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71335,7 +71335,7 @@
         <v>46300</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71408,7 +71408,7 @@
         <v>46300</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71481,7 +71481,7 @@
         <v>45602</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71554,7 +71554,7 @@
         <v>46301</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71627,7 +71627,7 @@
         <v>45784</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45351</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71773,7 +71773,7 @@
         <v>45545</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71846,7 +71846,7 @@
         <v>45736</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71919,7 +71919,7 @@
         <v>45273</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71992,7 +71992,7 @@
         <v>45505</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72065,7 +72065,7 @@
         <v>45582</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72138,7 +72138,7 @@
         <v>45702</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72211,7 +72211,7 @@
         <v>45505</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72284,7 +72284,7 @@
         <v>45428</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72357,7 +72357,7 @@
         <v>45516</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72430,7 +72430,7 @@
         <v>46303</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72503,7 +72503,7 @@
         <v>45789</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72576,7 +72576,7 @@
         <v>45789</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72649,7 +72649,7 @@
         <v>46303</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72722,7 +72722,7 @@
         <v>45552</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72795,7 +72795,7 @@
         <v>45791</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>45862</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>46303</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73014,7 +73014,7 @@
         <v>46303</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
         <v>46303</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73160,7 +73160,7 @@
         <v>45790</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
         <v>46303</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45188</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45518</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>45740</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73530,7 +73530,7 @@
         <v>46259</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73603,7 +73603,7 @@
         <v>45793</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73681,7 +73681,7 @@
         <v>45793</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73754,7 +73754,7 @@
         <v>45097</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>45097</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73910,7 +73910,7 @@
         <v>45518</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73983,7 +73983,7 @@
         <v>45594</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74056,7 +74056,7 @@
         <v>46304</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46212</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74207,7 +74207,7 @@
         <v>45796</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74280,7 +74280,7 @@
         <v>45533</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74353,7 +74353,7 @@
         <v>45796</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45796</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>46261</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74572,7 +74572,7 @@
         <v>45835</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74650,7 +74650,7 @@
         <v>45798</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74723,7 +74723,7 @@
         <v>45799</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74796,7 +74796,7 @@
         <v>45555</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74869,7 +74869,7 @@
         <v>46261</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74947,7 +74947,7 @@
         <v>46261</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75025,7 +75025,7 @@
         <v>45373</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75098,7 +75098,7 @@
         <v>45803</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75176,7 +75176,7 @@
         <v>45803</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75254,7 +75254,7 @@
         <v>45755</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75327,7 +75327,7 @@
         <v>46265</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75405,7 +75405,7 @@
         <v>46275</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75483,7 +75483,7 @@
         <v>46265</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75556,7 +75556,7 @@
         <v>45623</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75629,7 +75629,7 @@
         <v>46265</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75702,7 +75702,7 @@
         <v>46050</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75775,7 +75775,7 @@
         <v>46311</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75853,7 +75853,7 @@
         <v>45377</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75931,7 +75931,7 @@
         <v>45813</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76009,7 +76009,7 @@
         <v>45813</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         <v>45813</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76160,7 +76160,7 @@
         <v>46311</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76233,7 +76233,7 @@
         <v>45817</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76306,7 +76306,7 @@
         <v>45819</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76379,7 +76379,7 @@
         <v>45821</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76452,7 +76452,7 @@
         <v>45820</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76525,7 +76525,7 @@
         <v>45825</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76598,7 +76598,7 @@
         <v>45825</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76671,7 +76671,7 @@
         <v>45825</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76744,7 +76744,7 @@
         <v>45825</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45824</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>45824</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>46162</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77036,7 +77036,7 @@
         <v>45826</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77109,7 +77109,7 @@
         <v>45833</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77182,7 +77182,7 @@
         <v>45833</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>45833</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>45833</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>45833</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45833</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>45835</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45833</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>45840</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77771,7 +77771,7 @@
         <v>45840</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45202</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77922,7 +77922,7 @@
         <v>45733</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77995,7 +77995,7 @@
         <v>45847</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78073,7 +78073,7 @@
         <v>45849</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78151,7 +78151,7 @@
         <v>45849</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78229,7 +78229,7 @@
         <v>45853</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78302,7 +78302,7 @@
         <v>45776</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>44680</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78448,7 +78448,7 @@
         <v>45803</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>45874</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78599,7 +78599,7 @@
         <v>45393</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78672,7 +78672,7 @@
         <v>45874</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78750,7 +78750,7 @@
         <v>45877</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78823,7 +78823,7 @@
         <v>45877</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78896,7 +78896,7 @@
         <v>45881</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78969,7 +78969,7 @@
         <v>45882</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79042,7 +79042,7 @@
         <v>45881</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45883</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79188,7 +79188,7 @@
         <v>44160</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>44174</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79334,7 +79334,7 @@
         <v>45730</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79407,7 +79407,7 @@
         <v>45405</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79485,7 +79485,7 @@
         <v>45351</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79563,7 +79563,7 @@
         <v>45105</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79636,7 +79636,7 @@
         <v>45699</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79714,7 +79714,7 @@
         <v>45125</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79787,7 +79787,7 @@
         <v>45135</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79860,7 +79860,7 @@
         <v>44769</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79933,7 +79933,7 @@
         <v>44909</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80006,7 +80006,7 @@
         <v>45708</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80084,7 +80084,7 @@
         <v>45761</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>45761</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80240,7 +80240,7 @@
         <v>45771</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45814</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>45183</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>46056</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80542,7 +80542,7 @@
         <v>46072</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80620,7 +80620,7 @@
         <v>46089</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80698,7 +80698,7 @@
         <v>46141</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80776,7 +80776,7 @@
         <v>46198</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46007</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45476</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46052</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45534</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44911</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45222</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>46274</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45406</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>46283</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>46297</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>46311</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45825</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45831</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>45845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45231</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45321</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45525</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45194</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45359</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46027</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45894</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>46036</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45911</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45926</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45961</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44511</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45971</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46127</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46042</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45546</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>46127</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45985</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>46135</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45426</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>46231</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>46276</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>46276</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>46287</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>46112</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45365</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46296</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45784</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45490</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>46265</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46311</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45841</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44098</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>44495</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44536</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44497</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44610</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44488</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44638</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44790</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44795</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44795</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44791</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44824</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44833</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44733</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44692</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>44727</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44862</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44638</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44762</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44845</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44533</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44839</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44839</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>44841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44679</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44579</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44732</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44795</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44578</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44748</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45321</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45432</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44930</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>44651</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45425</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44826</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45555</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44719</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45596</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44893</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45517</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45351</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45093</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44602</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45299</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45321</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45344</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45231</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45201</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45478</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45321</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45344</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45518</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45225</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45677</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45363</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45321</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45225</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44991</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45173</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44872</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45398</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44922</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45194</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45352</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45513</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45755</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45453</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45300</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45362</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45201</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45562</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45653</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45539</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45033</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45337</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45757</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45275</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45412</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>44736</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45019</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45019</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45310</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44621</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>44944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45666</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45679</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45513</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45155</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45645</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45671</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45229</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46029</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>46033</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>46098</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45943</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45840</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45481</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45961</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45621</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45679</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45586</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45884</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45615</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45884</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46139</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45776</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45797</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45618</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>46049</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45841</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45659</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44529</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45264</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45888</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45916</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46139</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45181</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45700</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45895</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45894</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45989</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45259</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45896</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46139</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45784</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45637</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45898</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45379</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45884</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45124</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45611</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46036</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46048</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45957</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45440</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45314</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46062</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45077</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46025</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>46042</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>46057</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45567</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46084</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46083</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>46141</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>46141</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46048</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>46141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>46019</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45896</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45588</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>46037</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>46105</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46063</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46044</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45902</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45569</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45297</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45905</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45539</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45321</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45905</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>46106</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45107</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44644</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45939</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45590</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45908</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45245</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>46141</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45225</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45209</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46062</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45534</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45930</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46141</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45686</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45910</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46027</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46142</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45972</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45915</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45915</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>46052</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45915</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45916</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>44796</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>46146</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45919</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45358</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45920</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44928</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45923</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45923</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45923</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45923</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>46079</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45925</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>46148</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46149</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>46148</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45925</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45925</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>44515</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46148</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>46148</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44641</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45952</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45930</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46085</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45930</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45933</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45603</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45575</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45266</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45937</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45937</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44684</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>46064</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45539</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45937</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>46106</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45939</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45259</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45939</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44977</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45569</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45537</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45686</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45943</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45943</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44897</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45943</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45940</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>45940</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45943</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44762</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>46113</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45334</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45623</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>46105</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45539</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45930</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45646</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>46155</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45950</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45267</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45953</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45953</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>46048</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>44529</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45330</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45954</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>46055</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45174</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45957</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45251</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45672</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45958</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45958</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46157</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45245</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45960</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45960</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45960</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45961</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45960</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45960</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45541</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45721</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45167</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45965</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45520</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45965</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44964</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45537</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45967</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45967</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45967</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45971</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45537</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45616</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45971</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45971</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45968</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45973</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45972</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>46162</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45973</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45974</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45974</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45974</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45975</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>44746</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44914</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44960</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46167</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45737</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45985</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45397</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45985</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44911</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45985</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45985</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45985</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45264</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45985</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45985</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45986</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45618</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45986</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45987</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>45986</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45321</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45988</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45646</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45989</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45989</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44562</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45176</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45992</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45695</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45161</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>46105</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44807</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45994</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>46052</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45999</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45999</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46000</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46056</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46139</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>46105</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45264</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46000</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>46003</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45603</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45324</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45925</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45588</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>46009</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>46010</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46010</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46010</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46010</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45632</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44939</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45958</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45622</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46027</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46027</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46027</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46027</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46175</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>46175</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45617</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45639</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>44519</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46031</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45536</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>46030</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>46033</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46034</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46033</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>46027</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46033</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>46178</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>46036</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>46036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>46036</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>46141</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>46078</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45159</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>46042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46038</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>46178</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46042</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46042</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>46042</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>46178</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>46044</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>46044</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45737</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>46048</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>46048</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45546</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48673,7 +48673,7 @@
         <v>45267</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>46050</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46140</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45615</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45107</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>45107</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>44823</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>46121</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>44813</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46056</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45310</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46057</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44775</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45551</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45443</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45307</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46063</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46184</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46062</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>46062</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>46064</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46065</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46066</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46066</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46066</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45968</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46069</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46070</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46072</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46072</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46073</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>46073</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>46078</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45665</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46079</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>44638</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46085</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>46085</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46068</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>46086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>46090</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>46090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46190</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>44775</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>44775</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>44798</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>46190</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46070</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46189</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46191</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45672</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46043</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46191</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>46191</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>44544</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>46098</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>45625</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>46094</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45436</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45587</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>46196</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45618</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>46100</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>46195</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>46099</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>46098</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>46099</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46195</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46196</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>46195</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>46104</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>44790</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46105</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>45302</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>46106</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>44818</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>46106</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45097</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>46106</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55275,7 +55275,7 @@
         <v>46105</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45399</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45618</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46107</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55572,7 +55572,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55650,7 +55650,7 @@
         <v>45558</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>46050</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>46197</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46197</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46197</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>46140</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>46112</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>46198</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45772</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>46197</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>44953</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>46122</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>46122</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>45217</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46126</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>45321</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46126</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46125</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45518</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45518</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57213,7 +57213,7 @@
         <v>45072</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>44700</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>46127</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45593</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46129</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>46127</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>44818</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46203</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46133</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>46203</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>45105</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>46136</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45168</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45595</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>46029</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45671</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>45672</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>45176</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46203</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46136</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45555</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>44910</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45257</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45888</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>46025</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>46139</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46206</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>45236</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>46208</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45810</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45722</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45590</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>46205</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>46206</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>46206</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45483</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46209</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>44571</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>46211</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>46212</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>45230</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45243</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>46212</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60558,7 +60558,7 @@
         <v>45537</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>44939</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>44728</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60782,7 +60782,7 @@
         <v>45575</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60860,7 +60860,7 @@
         <v>44818</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45317</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61006,7 +61006,7 @@
         <v>44929</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>45644</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>46153</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>46164</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>46220</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45693</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>46108</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>46223</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         <v>46223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61683,7 +61683,7 @@
         <v>46224</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45476</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61829,7 +61829,7 @@
         <v>46273</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61907,7 +61907,7 @@
         <v>46230</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45642</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>44637</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62126,7 +62126,7 @@
         <v>45119</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62199,7 +62199,7 @@
         <v>45223</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>44806</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>46274</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>44519</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62496,7 +62496,7 @@
         <v>44875</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>45646</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62642,7 +62642,7 @@
         <v>46274</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>45582</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62793,7 +62793,7 @@
         <v>46275</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>46274</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>44841</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63022,7 +63022,7 @@
         <v>45775</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>45098</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>46233</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>46276</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45567</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>46279</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45182</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>46279</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45194</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63704,7 +63704,7 @@
         <v>46276</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63782,7 +63782,7 @@
         <v>46279</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>46276</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>45187</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>46237</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>45072</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64167,7 +64167,7 @@
         <v>45329</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64240,7 +64240,7 @@
         <v>46276</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>46280</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>46237</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
         <v>45204</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64537,7 +64537,7 @@
         <v>45516</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>46237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>46280</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64766,7 +64766,7 @@
         <v>46237</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>46239</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>46283</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64990,7 +64990,7 @@
         <v>45194</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65063,7 +65063,7 @@
         <v>45349</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45245</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65209,7 +65209,7 @@
         <v>44847</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65282,7 +65282,7 @@
         <v>45071</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65355,7 +65355,7 @@
         <v>45455</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>44930</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>44517</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45139</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65652,7 +65652,7 @@
         <v>46241</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65730,7 +65730,7 @@
         <v>46241</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65808,7 +65808,7 @@
         <v>45231</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>45231</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65954,7 +65954,7 @@
         <v>45534</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>45392</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66100,7 +66100,7 @@
         <v>44997</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>46198</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66251,7 +66251,7 @@
         <v>45002</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66324,7 +66324,7 @@
         <v>45259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>45625</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66470,7 +66470,7 @@
         <v>46241</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>46216</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>46244</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>46287</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>46244</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66855,7 +66855,7 @@
         <v>44746</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66928,7 +66928,7 @@
         <v>46241</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67006,7 +67006,7 @@
         <v>45600</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67079,7 +67079,7 @@
         <v>45232</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>46289</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67230,7 +67230,7 @@
         <v>45756</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67303,7 +67303,7 @@
         <v>44907</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45582</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>46248</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67532,7 +67532,7 @@
         <v>45744</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67605,7 +67605,7 @@
         <v>45190</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67678,7 +67678,7 @@
         <v>46171</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67756,7 +67756,7 @@
         <v>45176</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>44866</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>46248</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>45422</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68063,7 +68063,7 @@
         <v>45516</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68136,7 +68136,7 @@
         <v>45112</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68209,7 +68209,7 @@
         <v>46239</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>45334</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68355,7 +68355,7 @@
         <v>45173</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68428,7 +68428,7 @@
         <v>46203</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68506,7 +68506,7 @@
         <v>46293</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68584,7 +68584,7 @@
         <v>45586</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68662,7 +68662,7 @@
         <v>46098</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68735,7 +68735,7 @@
         <v>45733</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68808,7 +68808,7 @@
         <v>45525</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45525</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68954,7 +68954,7 @@
         <v>44551</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69027,7 +69027,7 @@
         <v>45321</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69100,7 +69100,7 @@
         <v>44804</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69173,7 +69173,7 @@
         <v>45686</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69246,7 +69246,7 @@
         <v>45666</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69319,7 +69319,7 @@
         <v>45946</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69392,7 +69392,7 @@
         <v>45771</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69465,7 +69465,7 @@
         <v>46296</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>46159</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69621,7 +69621,7 @@
         <v>45112</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>46134</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69772,7 +69772,7 @@
         <v>46296</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>46297</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69928,7 +69928,7 @@
         <v>46297</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70001,7 +70001,7 @@
         <v>45188</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>45560</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45666</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70220,7 +70220,7 @@
         <v>46300</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70293,7 +70293,7 @@
         <v>45776</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70366,7 +70366,7 @@
         <v>45776</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>46057</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>45779</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70590,7 +70590,7 @@
         <v>46300</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70663,7 +70663,7 @@
         <v>45616</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70736,7 +70736,7 @@
         <v>45782</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70809,7 +70809,7 @@
         <v>45279</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>45505</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>46300</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>45782</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>46258</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71179,7 +71179,7 @@
         <v>44799</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71257,7 +71257,7 @@
         <v>45910</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71335,7 +71335,7 @@
         <v>46300</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71408,7 +71408,7 @@
         <v>46300</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71481,7 +71481,7 @@
         <v>45602</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71554,7 +71554,7 @@
         <v>46301</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71627,7 +71627,7 @@
         <v>45784</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45351</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71773,7 +71773,7 @@
         <v>45545</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71846,7 +71846,7 @@
         <v>45736</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71919,7 +71919,7 @@
         <v>45273</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71992,7 +71992,7 @@
         <v>45505</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72065,7 +72065,7 @@
         <v>45582</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72138,7 +72138,7 @@
         <v>45702</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72211,7 +72211,7 @@
         <v>45505</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72284,7 +72284,7 @@
         <v>45428</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72357,7 +72357,7 @@
         <v>45516</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72430,7 +72430,7 @@
         <v>46303</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72503,7 +72503,7 @@
         <v>45789</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72576,7 +72576,7 @@
         <v>45789</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72649,7 +72649,7 @@
         <v>46303</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72722,7 +72722,7 @@
         <v>45552</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72795,7 +72795,7 @@
         <v>45791</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>45862</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>46303</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73014,7 +73014,7 @@
         <v>46303</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
         <v>46303</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73160,7 +73160,7 @@
         <v>45790</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
         <v>46303</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45188</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45518</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>45740</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73530,7 +73530,7 @@
         <v>46259</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73603,7 +73603,7 @@
         <v>45793</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73681,7 +73681,7 @@
         <v>45793</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73754,7 +73754,7 @@
         <v>45097</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>45097</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73910,7 +73910,7 @@
         <v>45518</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73983,7 +73983,7 @@
         <v>45594</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74056,7 +74056,7 @@
         <v>46304</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46212</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74207,7 +74207,7 @@
         <v>45796</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74280,7 +74280,7 @@
         <v>45533</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74353,7 +74353,7 @@
         <v>45796</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45796</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>46261</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74572,7 +74572,7 @@
         <v>45835</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74650,7 +74650,7 @@
         <v>45798</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74723,7 +74723,7 @@
         <v>45799</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74796,7 +74796,7 @@
         <v>45555</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74869,7 +74869,7 @@
         <v>46261</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74947,7 +74947,7 @@
         <v>46261</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75025,7 +75025,7 @@
         <v>45373</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75098,7 +75098,7 @@
         <v>45803</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75176,7 +75176,7 @@
         <v>45803</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75254,7 +75254,7 @@
         <v>45755</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75327,7 +75327,7 @@
         <v>46265</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75405,7 +75405,7 @@
         <v>46275</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75483,7 +75483,7 @@
         <v>46265</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75556,7 +75556,7 @@
         <v>45623</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75629,7 +75629,7 @@
         <v>46265</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75702,7 +75702,7 @@
         <v>46050</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75775,7 +75775,7 @@
         <v>46311</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75853,7 +75853,7 @@
         <v>45377</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75931,7 +75931,7 @@
         <v>45813</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76009,7 +76009,7 @@
         <v>45813</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         <v>45813</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76160,7 +76160,7 @@
         <v>46311</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76233,7 +76233,7 @@
         <v>45817</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76306,7 +76306,7 @@
         <v>45819</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76379,7 +76379,7 @@
         <v>45821</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76452,7 +76452,7 @@
         <v>45820</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76525,7 +76525,7 @@
         <v>45825</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76598,7 +76598,7 @@
         <v>45825</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76671,7 +76671,7 @@
         <v>45825</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76744,7 +76744,7 @@
         <v>45825</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45824</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>45824</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>46162</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77036,7 +77036,7 @@
         <v>45826</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77109,7 +77109,7 @@
         <v>45833</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77182,7 +77182,7 @@
         <v>45833</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>45833</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>45833</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>45833</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45833</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>45835</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45833</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>45840</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77771,7 +77771,7 @@
         <v>45840</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45202</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77922,7 +77922,7 @@
         <v>45733</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77995,7 +77995,7 @@
         <v>45847</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78073,7 +78073,7 @@
         <v>45849</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78151,7 +78151,7 @@
         <v>45849</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78229,7 +78229,7 @@
         <v>45853</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78302,7 +78302,7 @@
         <v>45776</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>44680</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78448,7 +78448,7 @@
         <v>45803</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>45874</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78599,7 +78599,7 @@
         <v>45393</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78672,7 +78672,7 @@
         <v>45874</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78750,7 +78750,7 @@
         <v>45877</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78823,7 +78823,7 @@
         <v>45877</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78896,7 +78896,7 @@
         <v>45881</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78969,7 +78969,7 @@
         <v>45882</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79042,7 +79042,7 @@
         <v>45881</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45883</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79188,7 +79188,7 @@
         <v>44160</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79261,7 +79261,7 @@
         <v>44174</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79334,7 +79334,7 @@
         <v>45730</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79407,7 +79407,7 @@
         <v>45405</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79485,7 +79485,7 @@
         <v>45351</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79563,7 +79563,7 @@
         <v>45105</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79636,7 +79636,7 @@
         <v>45699</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79714,7 +79714,7 @@
         <v>45125</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79787,7 +79787,7 @@
         <v>45135</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79860,7 +79860,7 @@
         <v>44769</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79933,7 +79933,7 @@
         <v>44909</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80006,7 +80006,7 @@
         <v>45708</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80084,7 +80084,7 @@
         <v>45761</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>45761</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80240,7 +80240,7 @@
         <v>45771</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45814</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>45183</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>46056</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80542,7 +80542,7 @@
         <v>46072</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80620,7 +80620,7 @@
         <v>46089</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80698,7 +80698,7 @@
         <v>46141</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80776,7 +80776,7 @@
         <v>46198</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46105</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44911</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45222</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45377</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>46283</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46297</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45845</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>46311</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>44529</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45406</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45033</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45077</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45008</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44620</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44845</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45894</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45411</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45911</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>46127</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45243</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45926</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45365</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45961</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45971</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>46211</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>45996</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46231</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>45490</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45524</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>46112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>46287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>46296</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>46127</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>46311</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45985</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>46316</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>46276</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>46276</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45321</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45694</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45279</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45194</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45359</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45231</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>44792</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44495</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44495</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44497</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44610</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44638</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44790</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>44795</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44795</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44791</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44824</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44833</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44733</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44692</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44727</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44862</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44638</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44762</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44845</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44533</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44839</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44839</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44797</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44841</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44679</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44579</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44732</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44537</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44795</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44748</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45302</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44775</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44775</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45321</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45267</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45700</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45894</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45539</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45329</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45895</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45733</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45264</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>45902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45884</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45883</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45905</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45258</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45905</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45225</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45266</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45908</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45229</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45230</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45910</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>46162</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45245</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45245</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44960</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45916</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45324</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44684</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45646</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45098</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>46139</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45920</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>46105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>46052</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45919</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45923</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>46167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44746</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45923</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45019</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45019</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44806</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45194</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45925</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45925</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45925</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>46056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45930</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46105</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45330</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45930</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45930</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45666</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>44930</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>44930</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44834</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45266</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45344</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45933</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45245</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>44866</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45590</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45937</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45618</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45399</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>46175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>46175</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45939</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45939</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45940</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45939</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45940</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45155</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45642</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45182</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45349</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45943</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45943</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45453</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45159</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45243</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44840</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45321</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45943</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45930</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>44953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45299</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44928</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>46078</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>44790</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45071</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>46178</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45586</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45537</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46178</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45544</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45950</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>46141</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45665</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45412</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>46178</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>46140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45953</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45953</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45954</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45243</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46121</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45957</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45957</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45968</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45958</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44736</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46184</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45960</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45960</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45321</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45960</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>46184</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>46189</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45961</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45569</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45002</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44551</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45965</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45672</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>46191</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46190</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44747</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45967</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46191</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45967</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45967</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44818</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46195</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45971</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45646</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>46195</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>46195</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>46195</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>46043</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45971</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45194</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>46197</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46197</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45225</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46140</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46197</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45209</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46197</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45973</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45974</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>46196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45973</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45194</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45232</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>46198</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45975</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45139</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44875</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45618</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45622</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45513</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45666</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45334</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>44517</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>46203</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>44939</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45516</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>46203</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>46203</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45259</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45742</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45297</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45352</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45986</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45985</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45985</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>46205</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45985</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45985</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>44911</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45986</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45321</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45775</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45987</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45253</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45588</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46209</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>46206</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46206</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46208</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>46206</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45541</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45625</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45989</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45989</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45615</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>46205</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45992</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>46211</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45994</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44819</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45231</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>46212</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45994</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45623</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>46212</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>44573</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45432</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45639</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45593</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45722</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46000</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46000</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45671</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45999</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>46000</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45999</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45776</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45693</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>46224</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46220</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>46153</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45776</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46164</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>46108</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45478</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>46223</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>46223</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45779</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45782</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45782</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>46003</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45505</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45925</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45616</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46230</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46233</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45702</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45310</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45516</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45784</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46010</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>46010</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>46010</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45582</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46279</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45545</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46237</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46279</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46009</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46010</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46237</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>46280</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>46280</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>46237</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>46237</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45602</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45351</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>44799</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45428</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45958</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45505</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45789</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45790</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45505</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46027</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>46027</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46027</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46027</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45789</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45791</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>46030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>46239</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45518</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45518</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45740</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46031</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>44818</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46033</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46033</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46033</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45188</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>46283</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46034</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45552</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46241</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46027</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45793</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46036</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>46036</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45796</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46036</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45796</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45533</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46198</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>45097</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45097</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46216</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>46241</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>46042</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>46241</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>46241</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>46287</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>46042</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>46042</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45436</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45796</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45793</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>46038</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>45594</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>46042</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>46044</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43537,7 +43537,7 @@
         <v>45798</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>46044</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>46048</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46244</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46244</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46049</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46050</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45799</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45755</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45803</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>46171</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45373</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45555</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45803</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44529</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>46289</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45623</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>46056</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46057</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>46062</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>46062</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>46248</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45377</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>46293</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>46248</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>46239</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>46064</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>46203</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>46064</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>45813</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>46063</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45813</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45813</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>46066</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46066</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>46065</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>46066</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46070</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>46098</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>46069</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45817</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45820</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45819</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>46072</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45821</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45824</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>46073</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>46296</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>46072</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45824</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45826</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>46078</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>45825</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>46296</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45825</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45825</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45825</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>46300</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>46085</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>46085</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45833</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45833</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45833</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>46086</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>45833</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45833</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>46068</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>46134</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45833</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45833</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45835</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>46090</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>46300</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>46090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>45910</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>46297</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>46300</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>46159</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>46057</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45840</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>46070</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45840</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>46300</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45546</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>46300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>45946</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>44939</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50305,7 +50305,7 @@
         <v>46098</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>46098</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>46099</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>46297</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>46099</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>46094</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>46100</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>45161</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50894,7 +50894,7 @@
         <v>45202</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50967,7 +50967,7 @@
         <v>45733</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>46105</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51118,7 +51118,7 @@
         <v>46104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>45236</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45847</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>46105</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>46105</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45849</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51654,7 +51654,7 @@
         <v>46106</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>46301</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45849</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>46050</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51956,7 +51956,7 @@
         <v>46258</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45853</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>46106</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>46107</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>46106</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45776</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45337</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45483</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>44680</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45537</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>46112</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45736</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52852,7 +52852,7 @@
         <v>45862</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>46303</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>46303</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>46303</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>46303</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>46261</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>46261</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45874</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>46303</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>46304</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>45874</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46125</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>46122</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>46122</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45393</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>46127</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>46126</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>46261</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>46126</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54274,7 +54274,7 @@
         <v>45803</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>46127</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46212</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>46303</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45877</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>45877</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>46265</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>44890</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45835</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54951,7 +54951,7 @@
         <v>45881</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45881</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>46129</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>46265</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55248,7 +55248,7 @@
         <v>45882</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>46133</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>46265</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45539</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>44914</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45884</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45646</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45551</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>45582</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45925</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>45518</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>45518</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45190</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45188</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>44922</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>44910</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45737</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45784</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>46136</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>46104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45525</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45525</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>46050</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45379</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45618</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46037</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>46162</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>45621</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46050</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>46098</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>46063</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>45481</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>45679</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>46057</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>46311</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>46311</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45939</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>45888</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45916</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45257</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58198,7 +58198,7 @@
         <v>45516</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45107</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46085</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45840</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58500,7 +58500,7 @@
         <v>46136</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
         <v>46139</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58651,7 +58651,7 @@
         <v>45440</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45567</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58797,7 +58797,7 @@
         <v>46042</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58870,7 +58870,7 @@
         <v>45595</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58943,7 +58943,7 @@
         <v>45989</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59016,7 +59016,7 @@
         <v>45961</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59094,7 +59094,7 @@
         <v>46027</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
         <v>45321</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45943</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>46029</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45560</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>46139</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>46035</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59605,7 +59605,7 @@
         <v>45201</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>46033</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59751,7 +59751,7 @@
         <v>45825</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>45653</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59902,7 +59902,7 @@
         <v>46050</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>46048</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>46139</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>46062</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60194,7 +60194,7 @@
         <v>46273</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60272,7 +60272,7 @@
         <v>46044</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60345,7 +60345,7 @@
         <v>46048</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60418,7 +60418,7 @@
         <v>45776</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>46139</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45810</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>44644</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>46315</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>45841</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>44964</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>46048</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61007,7 +61007,7 @@
         <v>46029</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>45243</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45797</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>44893</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>46083</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61372,7 +61372,7 @@
         <v>46025</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61445,7 +61445,7 @@
         <v>46025</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>46317</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61591,7 +61591,7 @@
         <v>45586</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>46049</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>46019</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>46141</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>46141</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>46083</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>45611</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>46274</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45799</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62253,7 +62253,7 @@
         <v>46274</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62331,7 +62331,7 @@
         <v>46062</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62404,7 +62404,7 @@
         <v>46105</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>45930</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62555,7 +62555,7 @@
         <v>46141</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>46276</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>46276</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>46276</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>46141</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62940,7 +62940,7 @@
         <v>46141</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>46142</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63096,7 +63096,7 @@
         <v>46132</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45896</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63247,7 +63247,7 @@
         <v>46052</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63325,7 +63325,7 @@
         <v>46276</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>44944</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63476,7 +63476,7 @@
         <v>46106</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>45957</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>46036</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>46070</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63773,7 +63773,7 @@
         <v>45686</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>46084</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>44529</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>46274</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>46146</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64148,7 +64148,7 @@
         <v>45757</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>46275</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45972</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>45968</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46275</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46079</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64596,7 +64596,7 @@
         <v>46146</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         <v>46148</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64747,7 +64747,7 @@
         <v>44977</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64820,7 +64820,7 @@
         <v>44977</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64893,7 +64893,7 @@
         <v>46148</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64971,7 +64971,7 @@
         <v>46148</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>46148</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>46148</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>44872</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65278,7 +65278,7 @@
         <v>44911</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>46149</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65429,7 +65429,7 @@
         <v>45321</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>45267</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65575,7 +65575,7 @@
         <v>45575</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65653,7 +65653,7 @@
         <v>46085</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>46064</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65799,7 +65799,7 @@
         <v>46106</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45397</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>46048</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66023,7 +66023,7 @@
         <v>46113</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>45182</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66174,7 +66174,7 @@
         <v>45558</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>45112</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>45952</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46055</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66471,7 +66471,7 @@
         <v>45562</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>46155</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66622,7 +66622,7 @@
         <v>46104</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66695,7 +66695,7 @@
         <v>46105</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>45755</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>45363</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>46157</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66992,7 +66992,7 @@
         <v>45314</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67065,7 +67065,7 @@
         <v>45307</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67138,7 +67138,7 @@
         <v>45603</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67211,7 +67211,7 @@
         <v>45671</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67284,7 +67284,7 @@
         <v>45672</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67357,7 +67357,7 @@
         <v>45119</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45107</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         <v>45672</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>45596</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>45645</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>45679</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67795,7 +67795,7 @@
         <v>44826</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67868,7 +67868,7 @@
         <v>44728</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67946,7 +67946,7 @@
         <v>44907</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68024,7 +68024,7 @@
         <v>45664</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
         <v>45625</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68175,7 +68175,7 @@
         <v>45636</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68248,7 +68248,7 @@
         <v>45615</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>45659</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68394,7 +68394,7 @@
         <v>45148</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68467,7 +68467,7 @@
         <v>45756</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68540,7 +68540,7 @@
         <v>45173</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68613,7 +68613,7 @@
         <v>45205</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68691,7 +68691,7 @@
         <v>44519</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68764,7 +68764,7 @@
         <v>45534</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>45021</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68910,7 +68910,7 @@
         <v>45637</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
         <v>45223</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69061,7 +69061,7 @@
         <v>44823</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69134,7 +69134,7 @@
         <v>45686</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69207,7 +69207,7 @@
         <v>45771</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69280,7 +69280,7 @@
         <v>45215</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69353,7 +69353,7 @@
         <v>45267</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69426,7 +69426,7 @@
         <v>45744</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69499,7 +69499,7 @@
         <v>45077</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69572,7 +69572,7 @@
         <v>45176</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69650,7 +69650,7 @@
         <v>44641</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69723,7 +69723,7 @@
         <v>45071</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69796,7 +69796,7 @@
         <v>44818</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69869,7 +69869,7 @@
         <v>45587</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69942,7 +69942,7 @@
         <v>44930</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70015,7 +70015,7 @@
         <v>45575</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70093,7 +70093,7 @@
         <v>45737</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70166,7 +70166,7 @@
         <v>45106</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
         <v>45105</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70312,7 +70312,7 @@
         <v>45251</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45536</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70458,7 +70458,7 @@
         <v>44804</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70531,7 +70531,7 @@
         <v>45518</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70604,7 +70604,7 @@
         <v>45321</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70677,7 +70677,7 @@
         <v>45167</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>45398</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>45245</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>44571</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>45251</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>44519</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>45520</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45425</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>44544</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71344,7 +71344,7 @@
         <v>44997</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71417,7 +71417,7 @@
         <v>45588</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71495,7 +71495,7 @@
         <v>44889</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71568,7 +71568,7 @@
         <v>45539</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71641,7 +71641,7 @@
         <v>45539</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71714,7 +71714,7 @@
         <v>45537</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71787,7 +71787,7 @@
         <v>45392</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71860,7 +71860,7 @@
         <v>45124</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71933,7 +71933,7 @@
         <v>44991</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72006,7 +72006,7 @@
         <v>45310</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72079,7 +72079,7 @@
         <v>45590</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72157,7 +72157,7 @@
         <v>45567</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72230,7 +72230,7 @@
         <v>45596</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72303,7 +72303,7 @@
         <v>45616</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>45617</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45632</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72522,7 +72522,7 @@
         <v>45264</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>45264</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72668,7 +72668,7 @@
         <v>45513</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72746,7 +72746,7 @@
         <v>45176</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72819,7 +72819,7 @@
         <v>45582</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45569</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>45539</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>45539</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73111,7 +73111,7 @@
         <v>45618</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73184,7 +73184,7 @@
         <v>44515</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73257,7 +73257,7 @@
         <v>45534</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73330,7 +73330,7 @@
         <v>45600</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73403,7 +73403,7 @@
         <v>45334</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73476,7 +73476,7 @@
         <v>45476</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73549,7 +73549,7 @@
         <v>45033</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73622,7 +73622,7 @@
         <v>44562</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73695,7 +73695,7 @@
         <v>45181</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73768,7 +73768,7 @@
         <v>45168</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73841,7 +73841,7 @@
         <v>45558</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73914,7 +73914,7 @@
         <v>45644</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73987,7 +73987,7 @@
         <v>45555</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>45623</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>45351</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74206,7 +74206,7 @@
         <v>45677</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74279,7 +74279,7 @@
         <v>45187</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74352,7 +74352,7 @@
         <v>45737</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74425,7 +74425,7 @@
         <v>45201</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74498,7 +74498,7 @@
         <v>45217</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74571,7 +74571,7 @@
         <v>45223</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74644,7 +74644,7 @@
         <v>45686</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>45560</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74790,7 +74790,7 @@
         <v>45672</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74863,7 +74863,7 @@
         <v>45666</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74936,7 +74936,7 @@
         <v>44638</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75009,7 +75009,7 @@
         <v>45085</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75082,7 +75082,7 @@
         <v>44637</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75155,7 +75155,7 @@
         <v>45225</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75228,7 +75228,7 @@
         <v>45721</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>44651</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>45455</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75452,7 +75452,7 @@
         <v>45176</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75525,7 +75525,7 @@
         <v>45686</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75598,7 +75598,7 @@
         <v>45253</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75671,7 +75671,7 @@
         <v>45161</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45275</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45772</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75900,7 +75900,7 @@
         <v>45107</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>45422</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>45168</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>45695</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76197,7 +76197,7 @@
         <v>44719</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76270,7 +76270,7 @@
         <v>44813</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76348,7 +76348,7 @@
         <v>44897</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76421,7 +76421,7 @@
         <v>45210</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76494,7 +76494,7 @@
         <v>44798</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76567,7 +76567,7 @@
         <v>45726</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76640,7 +76640,7 @@
         <v>45317</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76713,7 +76713,7 @@
         <v>45300</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76786,7 +76786,7 @@
         <v>44775</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76859,7 +76859,7 @@
         <v>45173</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76932,7 +76932,7 @@
         <v>45231</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77005,7 +77005,7 @@
         <v>45231</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77078,7 +77078,7 @@
         <v>45362</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77151,7 +77151,7 @@
         <v>45321</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77224,7 +77224,7 @@
         <v>45072</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77302,7 +77302,7 @@
         <v>45072</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77375,7 +77375,7 @@
         <v>45358</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77448,7 +77448,7 @@
         <v>45588</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77521,7 +77521,7 @@
         <v>45097</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77594,7 +77594,7 @@
         <v>44847</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77667,7 +77667,7 @@
         <v>45344</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77740,7 +77740,7 @@
         <v>45671</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77813,7 +77813,7 @@
         <v>45093</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77891,7 +77891,7 @@
         <v>45537</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77964,7 +77964,7 @@
         <v>45517</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78037,7 +78037,7 @@
         <v>45259</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78110,7 +78110,7 @@
         <v>44841</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78183,7 +78183,7 @@
         <v>45547</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78256,7 +78256,7 @@
         <v>45523</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78334,7 +78334,7 @@
         <v>45539</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78407,7 +78407,7 @@
         <v>44746</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78480,7 +78480,7 @@
         <v>45282</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78553,7 +78553,7 @@
         <v>44621</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78626,7 +78626,7 @@
         <v>44964</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78699,7 +78699,7 @@
         <v>45555</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78772,7 +78772,7 @@
         <v>44762</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78845,7 +78845,7 @@
         <v>44602</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78918,7 +78918,7 @@
         <v>44796</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78991,7 +78991,7 @@
         <v>44742</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79064,7 +79064,7 @@
         <v>44807</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79137,7 +79137,7 @@
         <v>45443</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79210,7 +79210,7 @@
         <v>45730</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79283,7 +79283,7 @@
         <v>44160</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79356,7 +79356,7 @@
         <v>44174</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79429,7 +79429,7 @@
         <v>45405</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79507,7 +79507,7 @@
         <v>45351</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79585,7 +79585,7 @@
         <v>45105</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79658,7 +79658,7 @@
         <v>45699</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79736,7 +79736,7 @@
         <v>45125</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79809,7 +79809,7 @@
         <v>45135</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79882,7 +79882,7 @@
         <v>44769</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79955,7 +79955,7 @@
         <v>44909</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80028,7 +80028,7 @@
         <v>45708</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80106,7 +80106,7 @@
         <v>45761</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80184,7 +80184,7 @@
         <v>45761</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80262,7 +80262,7 @@
         <v>45771</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80340,7 +80340,7 @@
         <v>45814</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80418,7 +80418,7 @@
         <v>45183</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80491,7 +80491,7 @@
         <v>46056</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80564,7 +80564,7 @@
         <v>46072</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80642,7 +80642,7 @@
         <v>46089</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80720,7 +80720,7 @@
         <v>46141</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80798,7 +80798,7 @@
         <v>46198</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>45728</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>46091</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45714</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44818</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>44874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46105</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45757</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45534</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44911</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45222</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>45377</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>46283</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45831</v>
       </c>
       <c r="E39" s="1" t="n">
-   